--- a/qa-artifacts/FoodHub-AI-Test-Analysis.xlsx
+++ b/qa-artifacts/FoodHub-AI-Test-Analysis.xlsx
@@ -400,19 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
-  <cols>
-    <col min="1" max="1" width="13.83203125" customWidth="1"/>
-    <col min="2" max="2" width="27.83203125" customWidth="1"/>
-    <col min="3" max="3" width="64.83203125" customWidth="1"/>
-    <col min="4" max="4" width="49.83203125" customWidth="1"/>
-    <col min="5" max="5" width="53.83203125" customWidth="1"/>
-    <col min="6" max="6" width="31.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="58.83203125" customWidth="1"/>
-    <col min="9" max="9" width="43.83203125" customWidth="1"/>
-    <col min="10" max="10" width="48.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:J6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -448,125 +436,174 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AI-FAIL-001</v>
+        <v>FOL-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Log capture</v>
+        <v>E2E Tests (Playwright)</v>
       </c>
       <c r="C2" t="str">
-        <v>Vitest, Pact, Playwright, Testcontainers, k6, and viewer logs retained</v>
+        <v>Timeout</v>
       </c>
       <c r="D2" t="str">
-        <v>Test logs and generated reports</v>
+        <v>2 occurrences: 'expect(locator).toHaveText: Timeout 5000ms exceeded' on #gateway-message; expected 'Payment declined for xxxx-xxxx-xxxx-8911.' but received 'Processing through FoodHub Payment Gateway...'</v>
       </c>
       <c r="E2" t="str">
-        <v>Unknown until logs are analyzed</v>
+        <v>Gateway UI update delayed; test assertion runs before the final 'declined' message replaces the processing state</v>
       </c>
       <c r="F2" t="str">
-        <v>Unknown</v>
+        <v>test</v>
       </c>
       <c r="G2" t="str">
-        <v>Medium</v>
+        <v>medium</v>
       </c>
       <c r="H2" t="str">
-        <v>Run analyzer and compare against observability artifacts</v>
+        <v>Replace immediate toHaveText with web-first assertions (waitForSelector with state 'attached' or 'visible') or poll for the expected final text with a generous timeout</v>
       </c>
       <c r="I2" t="str">
-        <v>Local fallback</v>
+        <v>sample-flaky-log.txt</v>
       </c>
       <c r="J2" t="str">
-        <v>deepseek-v4-pro high when FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AI-FAIL-002</v>
+        <v>FOL-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Pattern analysis</v>
+        <v>E2E Tests (Playwright)</v>
       </c>
       <c r="C3" t="str">
-        <v>Timeout, selector, startup, Pact, DB, and k6 signals scanned</v>
+        <v>Selector / UI locator</v>
       </c>
       <c r="D3" t="str">
-        <v>tests/fixtures/failureLogs/sample-flaky-log.txt</v>
+        <v>3 occurrences: locator '#gateway-message' text mismatch; received 'Processing through FoodHub Payment Gateway...' instead of expected declined message</v>
       </c>
       <c r="E3" t="str">
-        <v>Potential flaky test or environment issue</v>
+        <v>Locator is too generic; same element updates asynchronously during payment flow, causing assertion on intermediate state</v>
       </c>
       <c r="F3" t="str">
-        <v>Test or Environment</v>
+        <v>test</v>
       </c>
       <c r="G3" t="str">
-        <v>Medium</v>
+        <v>medium</v>
       </c>
       <c r="H3" t="str">
-        <v>Classify each hit and attach next diagnostic command</v>
+        <v>Use a more specific locator for the final declined message (e.g., text='Payment declined') or wait until the element contains the exact string before asserting</v>
       </c>
       <c r="I3" t="str">
-        <v>Local fallback</v>
+        <v>sample-flaky-log.txt</v>
       </c>
       <c r="J3" t="str">
-        <v>deepseek-v4-pro high when FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AI-FAIL-003</v>
+        <v>FOL-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Observability correlation</v>
+        <v>E2E Tests (Playwright)</v>
       </c>
       <c r="C4" t="str">
-        <v>Failure details compared with Firebase run history and request logs</v>
+        <v>Network / service startup</v>
       </c>
       <c r="D4" t="str">
-        <v>FoodHub-Observability-Dashboard.xlsx</v>
+        <v>1 occurrence: 'page.goto: net::ERR_CONNECTION_REFUSED at http://127.0.0.1:4173/'</v>
       </c>
       <c r="E4" t="str">
-        <v>Request-level regression or missing metric evidence</v>
+        <v>FoodHub app (port 4173) not listening when Playwright test starts; no startup health check performed</v>
       </c>
       <c r="F4" t="str">
-        <v>Product, Test, or Environment</v>
+        <v>environment</v>
       </c>
       <c r="G4" t="str">
-        <v>Medium</v>
+        <v>high</v>
       </c>
       <c r="H4" t="str">
-        <v>Correlate failed test timestamp with request logs</v>
+        <v>Add a pre-test step (e.g., wait-on http://127.0.0.1:4173/health or Playwright's webServer config with reuseExistingServer) to guarantee the app is ready before each e2e run</v>
       </c>
       <c r="I4" t="str">
-        <v>deepseek-v4-pro when live mode is enabled</v>
+        <v>sample-flaky-log.txt</v>
       </c>
       <c r="J4" t="str">
-        <v>deepseek-v4-pro high when FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>FOL-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>E2E Tests (Playwright)</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Payment gateway flow</v>
+      </c>
+      <c r="D5" t="str">
+        <v>10 occurrences across logged tests: redirect to gateway, payment processing, and message updates are brittle; one case timed out waiting for 'declined' message</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Synchronization issues between FoodHub and Payment Gateway; gateway callback or UI update may be slow, causing tests to observe intermediate processing states</v>
+      </c>
+      <c r="F5" t="str">
+        <v>environment</v>
+      </c>
+      <c r="G5" t="str">
+        <v>medium</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Wait for the gateway's final processing before asserting (e.g., waitForURL that returns to FoodHub, or waitForResponse on the order API before checking UI); verify gateway health as part of setup</v>
+      </c>
+      <c r="I5" t="str">
+        <v>sample-flaky-log.txt</v>
+      </c>
+      <c r="J5" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>FOL-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>E2E Tests (Playwright)</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Retry signal</v>
+      </c>
+      <c r="D6" t="str">
+        <v>1 occurrence: test 'customer can view menu, pay through the gateway, and receive an AI suggestion' failed with ERR_CONNECTION_REFUSED, then passed on Retry #1</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Environment not ready for initial attempt; retry succeeds only after the app fully starts</v>
+      </c>
+      <c r="F6" t="str">
+        <v>environment</v>
+      </c>
+      <c r="G6" t="str">
+        <v>high</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Remove dependency on retries by ensuring pre-test health checks; if retries are kept, investigate the exact readiness gap and add an explicit wait before the first navigation</v>
+      </c>
+      <c r="I6" t="str">
+        <v>sample-flaky-log.txt</v>
+      </c>
+      <c r="J6" t="str">
+        <v>DeepSeek</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
-  <cols>
-    <col min="1" max="1" width="13.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="64.83203125" customWidth="1"/>
-    <col min="5" max="5" width="55.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
-    <col min="7" max="7" width="64.83203125" customWidth="1"/>
-    <col min="8" max="8" width="33.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="7.83203125" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" customWidth="1"/>
-    <col min="13" max="13" width="38.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:M16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -611,31 +648,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AI-EDGE-001</v>
+        <v>FH-EDGE-001</v>
       </c>
       <c r="B2" t="str">
         <v>Edge Case</v>
       </c>
       <c r="C2" t="str">
-        <v>Menu</v>
+        <v>API</v>
       </c>
       <c r="D2" t="str">
-        <v>Menu API returns stable item contract</v>
+        <v>POST /order with negative quantity for a menu item</v>
       </c>
       <c r="E2" t="str">
-        <v>API contract breaking</v>
+        <v>Validation might not reject negative integer quantity, leading to incorrect pricing or downstream errors</v>
       </c>
       <c r="F2" t="str">
         <v>Integration</v>
       </c>
       <c r="G2" t="str">
-        <v>GET /menu returns items with id, name, price, and category</v>
+        <v>Response status 400 with error 'Invalid order'</v>
       </c>
       <c r="H2" t="str">
-        <v>Menu response fixture</v>
+        <v>Payload with items: [{ menuItemId: 'burger-classic', quantity: -1 }], valid paymentToken and customerName</v>
       </c>
       <c r="I2" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -644,39 +681,39 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="M2" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AI-EDGE-002</v>
+        <v>FH-EDGE-002</v>
       </c>
       <c r="B3" t="str">
         <v>Edge Case</v>
       </c>
       <c r="C3" t="str">
-        <v>Order</v>
+        <v>API</v>
       </c>
       <c r="D3" t="str">
-        <v>Order contains an unknown menu item</v>
+        <v>POST /order with zero quantity for a menu item</v>
       </c>
       <c r="E3" t="str">
-        <v>Invalid menu items</v>
+        <v>Zero quantity should be rejected per business logic but may pass validation</v>
       </c>
       <c r="F3" t="str">
         <v>Integration</v>
       </c>
       <c r="G3" t="str">
-        <v>POST /order returns 400 Invalid order</v>
+        <v>Response status 400 with error 'Invalid order'</v>
       </c>
       <c r="H3" t="str">
-        <v>Unknown item id payload</v>
+        <v>Payload with items: [{ menuItemId: 'burger-classic', quantity: 0 }], valid paymentToken and customerName</v>
       </c>
       <c r="I3" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -685,39 +722,39 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="M3" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AI-EDGE-003</v>
+        <v>FH-EDGE-003</v>
       </c>
       <c r="B4" t="str">
         <v>Edge Case</v>
       </c>
       <c r="C4" t="str">
-        <v>Order</v>
+        <v>API</v>
       </c>
       <c r="D4" t="str">
-        <v>Order contains no items</v>
+        <v>POST /order with non-integer quantity (e.g., 1.5)</v>
       </c>
       <c r="E4" t="str">
-        <v>Invalid empty orders</v>
+        <v>Zod schema int validation might accept if coerced? Should reject.</v>
       </c>
       <c r="F4" t="str">
         <v>Integration</v>
       </c>
       <c r="G4" t="str">
-        <v>POST /order returns 400 with empty-order detail</v>
+        <v>Response status 400 with error 'Invalid order'</v>
       </c>
       <c r="H4" t="str">
-        <v>Empty items payload</v>
+        <v>Payload with items: [{ menuItemId: 'burger-classic', quantity: 1.5 }], valid paymentToken and customerName</v>
       </c>
       <c r="I4" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -726,39 +763,39 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="M4" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AI-EDGE-004</v>
+        <v>FH-EDGE-004</v>
       </c>
       <c r="B5" t="str">
         <v>Edge Case</v>
       </c>
       <c r="C5" t="str">
-        <v>Totals</v>
+        <v>API</v>
       </c>
       <c r="D5" t="str">
-        <v>Order has mixed item quantities and decimal prices</v>
+        <v>POST /order with quantity exceeding upper boundary (21)</v>
       </c>
       <c r="E5" t="str">
-        <v>Incorrect totals</v>
+        <v>Boundary check at 20 may be missed, leading to order creation with excessive quantity</v>
       </c>
       <c r="F5" t="str">
-        <v>Unit</v>
+        <v>Integration</v>
       </c>
       <c r="G5" t="str">
-        <v>Total is rounded to two decimals and payment is charged once</v>
+        <v>Response status 400 with error 'Invalid order'</v>
       </c>
       <c r="H5" t="str">
-        <v>Mixed quantity order builder</v>
+        <v>Payload with items: [{ menuItemId: 'burger-classic', quantity: 21 }], valid paymentToken and customerName</v>
       </c>
       <c r="I5" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -767,261 +804,261 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="M5" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AI-EDGE-005</v>
+        <v>FH-MISS-001</v>
       </c>
       <c r="B6" t="str">
-        <v>Edge Case</v>
+        <v>Missing Scenario</v>
       </c>
       <c r="C6" t="str">
-        <v>Invoice</v>
+        <v>UI</v>
       </c>
       <c r="D6" t="str">
-        <v>Paid order invoice link shows transaction, order, card last 4, paid-via, and customer name</v>
+        <v>Customer sees error message when payment gateway is unreachable</v>
       </c>
       <c r="E6" t="str">
-        <v>Receipt/invoice evidence missing</v>
+        <v>User receives no feedback or a generic error when gateway is down, causing confusion</v>
       </c>
       <c r="F6" t="str">
         <v>E2E</v>
       </c>
       <c r="G6" t="str">
-        <v>Invoice panel opens from last transaction link and matches payment gateway data</v>
+        <v>Appropriate error message displayed (e.g., 'FoodHub Payment Gateway unavailable'), user can retry</v>
       </c>
       <c r="H6" t="str">
-        <v>Approved checkout fixture</v>
+        <v>Start app without payment gateway; use any valid card</v>
       </c>
       <c r="I6" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>Simulate gateway down by stopping port 4174 before checkout</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="M6" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>AI-MISS-001</v>
+        <v>FH-MISS-002</v>
       </c>
       <c r="B7" t="str">
         <v>Missing Scenario</v>
       </c>
       <c r="C7" t="str">
-        <v>Order</v>
+        <v>Observability</v>
       </c>
       <c r="D7" t="str">
-        <v>Duplicate items are submitted as separate order lines</v>
+        <v>Verify request logger writes structured log entry for POST /order</v>
       </c>
       <c r="E7" t="str">
-        <v>Duplicate lines can expose total-calculation mistakes</v>
+        <v>Missing observability data for order creation events, hampering debugging</v>
       </c>
       <c r="F7" t="str">
         <v>Integration</v>
       </c>
       <c r="G7" t="str">
-        <v>Submit the same menu item twice and verify totals remain correct</v>
+        <v>Log file contains entry with method POST, path /order, statusCode 201/400/402, durationMs, requestId</v>
       </c>
       <c r="H7" t="str">
-        <v>Duplicate item order builder</v>
+        <v>Send valid order; check qa-artifacts/observability/raw/request-logs.jsonl</v>
       </c>
       <c r="I7" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>Run test with NODE_ENV not 'test' to enable logger</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="M7" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>AI-MISS-002</v>
+        <v>FH-MISS-003</v>
       </c>
       <c r="B8" t="str">
         <v>Missing Scenario</v>
       </c>
       <c r="C8" t="str">
-        <v>Order</v>
+        <v>Payment</v>
       </c>
       <c r="D8" t="str">
-        <v>Large order at maximum accepted quantity</v>
+        <v>POST /order with invalid payment token format (e.g., 'invalid')</v>
       </c>
       <c r="E8" t="str">
-        <v>Boundary quantities can break validation or totals</v>
+        <v>Payment service may throw unexpected error or not return 402</v>
       </c>
       <c r="F8" t="str">
         <v>Integration</v>
       </c>
       <c r="G8" t="str">
-        <v>Submit quantity 20 and verify the order is accepted with correct total</v>
+        <v>Response status 402 with error 'Payment failed' and details message</v>
       </c>
       <c r="H8" t="str">
-        <v>Boundary quantity order builder</v>
+        <v>Payload with paymentToken: 'invalid'</v>
       </c>
       <c r="I8" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>FakePaymentGateway returns failed if token does not start with 'gateway_paid_' or 'tok_success'</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="M8" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>AI-MISS-003</v>
+        <v>FH-MISS-004</v>
       </c>
       <c r="B9" t="str">
         <v>Missing Scenario</v>
       </c>
       <c r="C9" t="str">
-        <v>Order</v>
+        <v>Persistence</v>
       </c>
       <c r="D9" t="str">
-        <v>Invalid payload shapes are rejected predictably</v>
+        <v>Verify paid order is persisted and retrievable from PostgreSQL via Testcontainers</v>
       </c>
       <c r="E9" t="str">
-        <v>Malformed clients should receive predictable errors</v>
+        <v>Order data may not be saved, leading to loss of transaction records</v>
       </c>
       <c r="F9" t="str">
-        <v>Integration</v>
+        <v>Integration (Testcontainers)</v>
       </c>
       <c r="G9" t="str">
-        <v>Submit items as an object instead of an array and verify 400 response</v>
+        <v>After successful POST /order, query database returns saved receipt with same orderId</v>
       </c>
       <c r="H9" t="str">
-        <v>Malformed payload fixture</v>
+        <v>Real PostgreSQL container; insert order, then read back</v>
       </c>
       <c r="I9" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>Requires OrderRepository with save method; must be implemented and tested</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="M9" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>AI-COV-001</v>
+        <v>FH-EXPN-001</v>
       </c>
       <c r="B10" t="str">
         <v>Coverage Expansion</v>
       </c>
       <c r="C10" t="str">
-        <v>Payment</v>
+        <v>API</v>
       </c>
       <c r="D10" t="str">
-        <v>Gateway cancellation should not create paid orders</v>
+        <v>POST /order with all available menu items in a single order</v>
       </c>
       <c r="E10" t="str">
-        <v>Cancelled payments must not create orders</v>
+        <v>Total calculation may overflow or misbehave with many line items</v>
       </c>
       <c r="F10" t="str">
-        <v>E2E</v>
+        <v>Integration</v>
       </c>
       <c r="G10" t="str">
-        <v>Cancel gateway flow and verify no order is created</v>
+        <v>Status 201 with correct total sum of all items prices times quantities (each quantity 1)</v>
       </c>
       <c r="H10" t="str">
-        <v>Cancelled checkout fixture</v>
+        <v>Payload with items array containing every menu item id with quantity 1</v>
       </c>
       <c r="I10" t="str">
-        <v>Candidate</v>
+        <v>To Do</v>
       </c>
       <c r="J10" t="str">
         <v/>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>Ensures pricing logic handles full menu</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="M10" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>AI-COV-002</v>
+        <v>FH-EXPN-002</v>
       </c>
       <c r="B11" t="str">
         <v>Coverage Expansion</v>
       </c>
       <c r="C11" t="str">
-        <v>Observability</v>
+        <v>Visual</v>
       </c>
       <c r="D11" t="str">
-        <v>Dashboard refresh and truncate controls have script-level verification</v>
+        <v>Visual regression test on mobile viewport (iPhone 12)</v>
       </c>
       <c r="E11" t="str">
-        <v>Observability drift</v>
+        <v>UI may break on smaller screens, text overflow, layout shift</v>
       </c>
       <c r="F11" t="str">
-        <v>Report</v>
+        <v>E2E (Playwright)</v>
       </c>
       <c r="G11" t="str">
-        <v>Refresh Firebase-backed dashboard and verify generated workbook sheets</v>
+        <v>Screenshots match baseline for menu, cart, and gateway states on mobile</v>
       </c>
       <c r="H11" t="str">
-        <v>Observability metrics fixture</v>
+        <v>Use Playwright device emulation for iPhone 12</v>
       </c>
       <c r="I11" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>Add new snapshot files for mobile</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="M11" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>AI-COV-003</v>
+        <v>FH-EXPN-003</v>
       </c>
       <c r="B12" t="str">
         <v>Coverage Expansion</v>
@@ -1030,59 +1067,210 @@
         <v>Load</v>
       </c>
       <c r="D12" t="str">
-        <v>API handles repeated browse-and-order traffic</v>
+        <v>Load test with 50 concurrent virtual users creating orders</v>
       </c>
       <c r="E12" t="str">
-        <v>Performance regression</v>
+        <v>System may exceed p95 latency or failure thresholds under high concurrency</v>
       </c>
       <c r="F12" t="str">
-        <v>Load</v>
+        <v>Load (k6)</v>
       </c>
       <c r="G12" t="str">
-        <v>k6 thresholds pass for p95 latency, HTTP failures, and paid-order failures</v>
+        <v>http_req_failed rate &lt; 0.05, p95 latency &lt; 500ms, foodhub_order_failures rate &lt; 0.02</v>
       </c>
       <c r="H12" t="str">
-        <v>k6 seeded load data</v>
+        <v>Set VUS=50, ramp-up 30s, steady 60s; use random order templates</v>
       </c>
       <c r="I12" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>Run after ensuring API and gateway are on HOST=0.0.0.0</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="M12" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>FH-EXPN-004</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Coverage Expansion</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Pact contract test verifying consumer (Web UI) can consume provider (API) endpoints correctly</v>
+      </c>
+      <c r="E13" t="str">
+        <v>API contract regressions not detected during CI if only integration tests run</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Contract (Pact)</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Pact verification passes for all interactions defined in consumer tests</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Define Pact interactions for menu and order endpoints; provider state setup</v>
+      </c>
+      <c r="I13" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>Implementation detail: use @pact-foundation/pact</v>
+      </c>
+      <c r="L13" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="M13" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>FH-EXPN-005</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Coverage Expansion</v>
+      </c>
+      <c r="C14" t="str">
+        <v>AI Recommendation</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Verify aiSuggestion is empty or defaults when cart is empty or consists only of drinks</v>
+      </c>
+      <c r="E14" t="str">
+        <v>AI suggestion logic may generate weird recommendations for edge cases</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Unit/Integration</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Recommended string is sensible and not empty for standard orders; for empty cart or drinks-only, suggestion may be absent or generic</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Order with only drink items (e.g., cola-zero, lemonade)</v>
+      </c>
+      <c r="I14" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>Check recommendationService logic in src/services/recommendationService.ts</v>
+      </c>
+      <c r="L14" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="M14" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>FH-EXPN-006</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Coverage Expansion</v>
+      </c>
+      <c r="C15" t="str">
+        <v>UI</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Checkout button disabled state when cart is empty</v>
+      </c>
+      <c r="E15" t="str">
+        <v>User may be able to click checkout with empty cart if button enabled incorrectly</v>
+      </c>
+      <c r="F15" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Checkout button should be disabled and have aria-disabled attribute</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Navigate to page with empty cart</v>
+      </c>
+      <c r="I15" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>Use expect(page.locator('#checkout-button')).toBeDisabled()</v>
+      </c>
+      <c r="L15" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="M15" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>FH-MISS-005</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Invoice</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Invoice link not available after page refresh mid-session</v>
+      </c>
+      <c r="E16" t="str">
+        <v>User loses ability to view invoice after browser refresh since state is stored in memory only</v>
+      </c>
+      <c r="F16" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="G16" t="str">
+        <v>After refresh, invoice link panel should be hidden (no invoice state persisted); user may need to re-order to see invoice</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Complete an order, then refresh the page; verify invoice link not present</v>
+      </c>
+      <c r="I16" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>Not a bug but a UX gap; consider persisting last invoice in localStorage</v>
+      </c>
+      <c r="L16" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="M16" t="str">
+        <v>DeepSeek</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
-  <cols>
-    <col min="1" max="1" width="13.83203125" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="39.83203125" customWidth="1"/>
-    <col min="6" max="6" width="43.83203125" customWidth="1"/>
-    <col min="7" max="7" width="56.83203125" customWidth="1"/>
-    <col min="8" max="8" width="34.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="38.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:K12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1121,217 +1309,392 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AI-DATA-001</v>
+        <v>TD-001</v>
       </c>
       <c r="B2" t="str">
-        <v>AI-EDGE-004</v>
+        <v>EDGE-001</v>
       </c>
       <c r="C2" t="str">
         <v>Edge Case</v>
       </c>
       <c r="D2" t="str">
-        <v>Randomized mixed order</v>
+        <v>Order payload</v>
       </c>
       <c r="E2" t="str">
-        <v>createRandomOrder(seed)</v>
+        <v>createOrder with quantity 1</v>
       </c>
       <c r="F2" t="str">
-        <v>Seeded deterministic mixed menu items</v>
+        <v>{"items":[{"menuItemId":"burger-classic","quantity":1}],"paymentToken":"gateway_paid_test123","customerName":"Test"}</v>
       </c>
       <c r="G2" t="str">
-        <v>Broaden order combinations without shared mutable data</v>
+        <v>Verify that the minimum valid quantity (1) is accepted and correctly priced</v>
       </c>
       <c r="H2" t="str">
-        <v>Mixed-quantity total validation</v>
+        <v>Integration test</v>
       </c>
       <c r="I2" t="str">
-        <v>Implemented</v>
+        <v>suggested</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>Manual analysis</v>
       </c>
       <c r="K2" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AI-DATA-002</v>
+        <v>TD-002</v>
       </c>
       <c r="B3" t="str">
-        <v>AI-MISS-002</v>
+        <v>EDGE-002</v>
       </c>
       <c r="C3" t="str">
-        <v>Missing Scenario</v>
+        <v>Edge Case</v>
       </c>
       <c r="D3" t="str">
-        <v>Boundary quantity</v>
+        <v>Order payload</v>
       </c>
       <c r="E3" t="str">
-        <v>createBoundaryQuantityOrder(20)</v>
+        <v>createBoundaryQuantityOrder(20) (already exists)</v>
       </c>
       <c r="F3" t="str">
-        <v>burger-classic x 20</v>
+        <v>{"items":[{"menuItemId":"burger-classic","quantity":20}],"paymentToken":"gateway_paid_test456","customerName":"Boundary"}</v>
       </c>
       <c r="G3" t="str">
-        <v>Validate upper accepted quantity</v>
+        <v>Confirm boundary quantity 20 is accepted and total is correct (already covered by existing test, listed for completeness)</v>
       </c>
       <c r="H3" t="str">
-        <v>Large order missing scenario</v>
+        <v>Integration test</v>
       </c>
       <c r="I3" t="str">
-        <v>Implemented</v>
+        <v>covered</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>Existing test</v>
       </c>
       <c r="K3" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AI-DATA-003</v>
+        <v>TD-003</v>
       </c>
       <c r="B4" t="str">
-        <v>AI-MISS-001</v>
+        <v>MISS-001</v>
       </c>
       <c r="C4" t="str">
         <v>Missing Scenario</v>
       </c>
       <c r="D4" t="str">
-        <v>Duplicate item lines</v>
+        <v>Payment token</v>
       </c>
       <c r="E4" t="str">
-        <v>createDuplicateItemOrder()</v>
+        <v>createOrder with paymentToken "tok_success"</v>
       </c>
       <c r="F4" t="str">
-        <v>burger-classic x 1 and burger-classic x 2</v>
+        <v>{"items":[{"menuItemId":"lemonade","quantity":2}],"paymentToken":"tok_success","customerName":"TokenSuccess"}</v>
       </c>
       <c r="G4" t="str">
-        <v>Validate totals across repeated menu item ids</v>
+        <v>Test that the legacy success token 'tok_success' is handled correctly and returns a paid receipt</v>
       </c>
       <c r="H4" t="str">
-        <v>Duplicate items missing scenario</v>
+        <v>Integration test</v>
       </c>
       <c r="I4" t="str">
-        <v>Implemented</v>
+        <v>suggested</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>Code review – paymentService accepts 'tok_success' but no integration test uses it</v>
       </c>
       <c r="K4" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AI-DATA-004</v>
+        <v>TD-004</v>
       </c>
       <c r="B5" t="str">
-        <v>AI-EDGE-005</v>
+        <v>MISS-002</v>
       </c>
       <c r="C5" t="str">
-        <v>Edge Case</v>
+        <v>Missing Scenario</v>
       </c>
       <c r="D5" t="str">
-        <v>Invoice customer</v>
+        <v>Order payload</v>
       </c>
       <c r="E5" t="str">
-        <v>createApprovedCheckout().customerName</v>
+        <v>createOrder with customerName set to whitespace-only string</v>
       </c>
       <c r="F5" t="str">
-        <v>FoodHub Demo User</v>
+        <v>{"items":[{"menuItemId":"wrap-veggie","quantity":1}],"paymentToken":"gateway_paid_test789","customerName":"   "}</v>
       </c>
       <c r="G5" t="str">
-        <v>Verify invoice customer-name publishing</v>
+        <v>Ensure that a customerName consisting only of whitespace is rejected (Zod .trim().min(1))</v>
       </c>
       <c r="H5" t="str">
-        <v>Invoice receipt validation</v>
+        <v>Integration test</v>
       </c>
       <c r="I5" t="str">
-        <v>Implemented</v>
+        <v>suggested</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>Code analysis – schema uses .trim().min(1) but not tested</v>
       </c>
       <c r="K5" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AI-DATA-005</v>
+        <v>TD-005</v>
       </c>
       <c r="B6" t="str">
-        <v>AI-COV-003</v>
+        <v>EDGE-003</v>
       </c>
       <c r="C6" t="str">
-        <v>Coverage Expansion</v>
+        <v>Edge Case</v>
       </c>
       <c r="D6" t="str">
-        <v>Load traffic</v>
+        <v>Order payload</v>
       </c>
       <c r="E6" t="str">
-        <v>k6 __VU/__ITER payment token</v>
+        <v>createOrder with quantity 0</v>
       </c>
       <c r="F6" t="str">
-        <v>gateway_paid_load_1_1</v>
+        <v>{"items":[{"menuItemId":"burger-classic","quantity":0}],"paymentToken":"gateway_paid_test000","customerName":"ZeroQty"}</v>
       </c>
       <c r="G6" t="str">
-        <v>Avoid payment-token collisions during load execution</v>
+        <v>Verify that quantity 0 is rejected (z.number().int().positive())</v>
       </c>
       <c r="H6" t="str">
-        <v>Load coverage expansion</v>
+        <v>Integration test</v>
       </c>
       <c r="I6" t="str">
-        <v>Implemented</v>
+        <v>suggested</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>Manual analysis – positive constraint not covered</v>
       </c>
       <c r="K6" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>AI-DATA-006</v>
+        <v>TD-006</v>
       </c>
       <c r="B7" t="str">
-        <v>AI-COV-002</v>
+        <v>EDGE-004</v>
       </c>
       <c r="C7" t="str">
+        <v>Edge Case</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Order payload</v>
+      </c>
+      <c r="E7" t="str">
+        <v>createOrder with negative quantity</v>
+      </c>
+      <c r="F7" t="str">
+        <v>{"items":[{"menuItemId":"cola-zero","quantity":-3}],"paymentToken":"gateway_paid_test111","customerName":"NegativeQty"}</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Ensure negative quantity is rejected by Zod or validation logic</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Integration test</v>
+      </c>
+      <c r="I7" t="str">
+        <v>suggested</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Manual analysis – negative integer not tested</v>
+      </c>
+      <c r="K7" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TD-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>MISS-003</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Order payload</v>
+      </c>
+      <c r="E8" t="str">
+        <v>createOrder with null items element</v>
+      </c>
+      <c r="F8" t="str">
+        <v>{"items":[null],"paymentToken":"gateway_paid_test222","customerName":"NullItem"}</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Check that an array containing null is rejected with 400 error</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Integration test</v>
+      </c>
+      <c r="I8" t="str">
+        <v>suggested</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Code review – Zod array of objects, null element not tested</v>
+      </c>
+      <c r="K8" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>TD-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>COV-001</v>
+      </c>
+      <c r="C9" t="str">
         <v>Coverage Expansion</v>
       </c>
-      <c r="D7" t="str">
-        <v>Observability metrics</v>
-      </c>
-      <c r="E7" t="str">
-        <v>latest-observability-metrics.json</v>
-      </c>
-      <c r="F7" t="str">
-        <v>requestCount, errorCount, p95DurationMs</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Feed Firebase and charted dashboard</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Observability coverage expansion</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Implemented</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+      <c r="D9" t="str">
+        <v>Order payload</v>
+      </c>
+      <c r="E9" t="str">
+        <v>createRandomOrder(10) or a new builder createLargeDistinctOrder</v>
+      </c>
+      <c r="F9" t="str">
+        <v>{"items":[{"menuItemId":"burger-classic","quantity":1},{"menuItemId":"wrap-veggie","quantity":2},{"menuItemId":"lemonade","quantity":1},{"menuItemId":"cola-zero","quantity":1},{"menuItemId":"fries-large","quantity":1}],"paymentToken":"gateway_paid_test333","customerName":"LargeOrder"}</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Verify that an order with many unique items (e.g., 5+ distinct menu items) processes correctly and total is accurate</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Integration test / Load test</v>
+      </c>
+      <c r="I9" t="str">
+        <v>suggested</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Coverage analysis – only small orders tested</v>
+      </c>
+      <c r="K9" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TD-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>COV-002</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Coverage Expansion</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Order payload</v>
+      </c>
+      <c r="E10" t="str">
+        <v>createOrder with a price that causes floating point rounding</v>
+      </c>
+      <c r="F10" t="str">
+        <v>{"items":[{"menuItemId":"items with price 0.10","quantity":3}],"paymentToken":"gateway_paid_test444","customerName":"RoundingTest"}</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Ensure roundMoney correctly handles floating point arithmetic (e.g., 0.10 * 3 = 0.30, not 0.30000000000000004)</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Integration test</v>
+      </c>
+      <c r="I10" t="str">
+        <v>suggested</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Code analysis – roundMoney uses Number.EPSILON, no explicit test</v>
+      </c>
+      <c r="K10" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>TD-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MISS-004</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Payment token</v>
+      </c>
+      <c r="E11" t="str">
+        <v>createOrder with paymentToken missing from request</v>
+      </c>
+      <c r="F11" t="str">
+        <v>{"items":[{"menuItemId":"fries-large","quantity":1}],"customerName":"NoToken"}</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Validate that a missing paymentToken field is caught by Zod (z.string().min(1)) and returns 400</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Integration test</v>
+      </c>
+      <c r="I11" t="str">
+        <v>suggested</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Manual analysis – required field not tested for absence</v>
+      </c>
+      <c r="K11" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>TD-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>EDGE-005</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Edge Case</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Order payload</v>
+      </c>
+      <c r="E12" t="str">
+        <v>createOrder with customerName of length 255</v>
+      </c>
+      <c r="F12" t="str">
+        <v>{"items":[{"menuItemId":"burger-classic","quantity":1}],"paymentToken":"gateway_paid_test555","customerName":"a... (255 characters)"}</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Test that a very long customerName (255 chars) is accepted or rejected appropriately (no length constraint in schema, but may cause DB issues)</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Integration test</v>
+      </c>
+      <c r="I12" t="str">
+        <v>suggested</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Edge case analysis – no length validation on customerName</v>
+      </c>
+      <c r="K12" t="str">
+        <v>N/A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K12"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1340,9 +1703,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="47.83203125" customWidth="1"/>
-    <col min="3" max="3" width="64.83203125" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="90.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1372,7 +1735,7 @@
         <v>DeepSeek API key</v>
       </c>
       <c r="B3" t="str">
-        <v>Not configured</v>
+        <v>Configured</v>
       </c>
       <c r="C3" t="str">
         <v>DeepSeek bearer token loaded from Firestore foodhub-6ba1c/deepSeek/ooz80WHRgmUV3WseQDnF/api-key</v>

--- a/qa-artifacts/FoodHub-AI-Test-Analysis.xlsx
+++ b/qa-artifacts/FoodHub-AI-Test-Analysis.xlsx
@@ -400,7 +400,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J4"/>
+  <cols>
+    <col min="1" max="1" width="13.83203125" customWidth="1"/>
+    <col min="2" max="2" width="27.83203125" customWidth="1"/>
+    <col min="3" max="3" width="64.83203125" customWidth="1"/>
+    <col min="4" max="4" width="49.83203125" customWidth="1"/>
+    <col min="5" max="5" width="53.83203125" customWidth="1"/>
+    <col min="6" max="6" width="31.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="58.83203125" customWidth="1"/>
+    <col min="9" max="9" width="43.83203125" customWidth="1"/>
+    <col min="10" max="10" width="48.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,174 +448,125 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FOL-001</v>
+        <v>AI-FAIL-001</v>
       </c>
       <c r="B2" t="str">
-        <v>E2E Tests (Playwright)</v>
+        <v>Log capture</v>
       </c>
       <c r="C2" t="str">
-        <v>Timeout</v>
+        <v>Vitest, Pact, Playwright, Testcontainers, k6, and viewer logs retained</v>
       </c>
       <c r="D2" t="str">
-        <v>2 occurrences: 'expect(locator).toHaveText: Timeout 5000ms exceeded' on #gateway-message; expected 'Payment declined for xxxx-xxxx-xxxx-8911.' but received 'Processing through FoodHub Payment Gateway...'</v>
+        <v>Test logs and generated reports</v>
       </c>
       <c r="E2" t="str">
-        <v>Gateway UI update delayed; test assertion runs before the final 'declined' message replaces the processing state</v>
+        <v>Unknown until logs are analyzed</v>
       </c>
       <c r="F2" t="str">
-        <v>test</v>
+        <v>Unknown</v>
       </c>
       <c r="G2" t="str">
-        <v>medium</v>
+        <v>Medium</v>
       </c>
       <c r="H2" t="str">
-        <v>Replace immediate toHaveText with web-first assertions (waitForSelector with state 'attached' or 'visible') or poll for the expected final text with a generous timeout</v>
+        <v>Run analyzer and compare against observability artifacts</v>
       </c>
       <c r="I2" t="str">
-        <v>sample-flaky-log.txt</v>
+        <v>Local fallback</v>
       </c>
       <c r="J2" t="str">
-        <v>DeepSeek</v>
+        <v>deepseek-v4-pro high when FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FOL-002</v>
+        <v>AI-FAIL-002</v>
       </c>
       <c r="B3" t="str">
-        <v>E2E Tests (Playwright)</v>
+        <v>Pattern analysis</v>
       </c>
       <c r="C3" t="str">
-        <v>Selector / UI locator</v>
+        <v>Timeout, selector, startup, Pact, DB, and k6 signals scanned</v>
       </c>
       <c r="D3" t="str">
-        <v>3 occurrences: locator '#gateway-message' text mismatch; received 'Processing through FoodHub Payment Gateway...' instead of expected declined message</v>
+        <v>tests/fixtures/failureLogs/sample-flaky-log.txt</v>
       </c>
       <c r="E3" t="str">
-        <v>Locator is too generic; same element updates asynchronously during payment flow, causing assertion on intermediate state</v>
+        <v>Potential flaky test or environment issue</v>
       </c>
       <c r="F3" t="str">
-        <v>test</v>
+        <v>Test or Environment</v>
       </c>
       <c r="G3" t="str">
-        <v>medium</v>
+        <v>Medium</v>
       </c>
       <c r="H3" t="str">
-        <v>Use a more specific locator for the final declined message (e.g., text='Payment declined') or wait until the element contains the exact string before asserting</v>
+        <v>Classify each hit and attach next diagnostic command</v>
       </c>
       <c r="I3" t="str">
-        <v>sample-flaky-log.txt</v>
+        <v>Local fallback</v>
       </c>
       <c r="J3" t="str">
-        <v>DeepSeek</v>
+        <v>deepseek-v4-pro high when FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FOL-003</v>
+        <v>AI-FAIL-003</v>
       </c>
       <c r="B4" t="str">
-        <v>E2E Tests (Playwright)</v>
+        <v>Observability correlation</v>
       </c>
       <c r="C4" t="str">
-        <v>Network / service startup</v>
+        <v>Failure details compared with Firebase run history and request logs</v>
       </c>
       <c r="D4" t="str">
-        <v>1 occurrence: 'page.goto: net::ERR_CONNECTION_REFUSED at http://127.0.0.1:4173/'</v>
+        <v>FoodHub-Observability-Dashboard.xlsx</v>
       </c>
       <c r="E4" t="str">
-        <v>FoodHub app (port 4173) not listening when Playwright test starts; no startup health check performed</v>
+        <v>Request-level regression or missing metric evidence</v>
       </c>
       <c r="F4" t="str">
-        <v>environment</v>
+        <v>Product, Test, or Environment</v>
       </c>
       <c r="G4" t="str">
-        <v>high</v>
+        <v>Medium</v>
       </c>
       <c r="H4" t="str">
-        <v>Add a pre-test step (e.g., wait-on http://127.0.0.1:4173/health or Playwright's webServer config with reuseExistingServer) to guarantee the app is ready before each e2e run</v>
+        <v>Correlate failed test timestamp with request logs</v>
       </c>
       <c r="I4" t="str">
-        <v>sample-flaky-log.txt</v>
+        <v>deepseek-v4-pro when live mode is enabled</v>
       </c>
       <c r="J4" t="str">
-        <v>DeepSeek</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>FOL-004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>E2E Tests (Playwright)</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Payment gateway flow</v>
-      </c>
-      <c r="D5" t="str">
-        <v>10 occurrences across logged tests: redirect to gateway, payment processing, and message updates are brittle; one case timed out waiting for 'declined' message</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Synchronization issues between FoodHub and Payment Gateway; gateway callback or UI update may be slow, causing tests to observe intermediate processing states</v>
-      </c>
-      <c r="F5" t="str">
-        <v>environment</v>
-      </c>
-      <c r="G5" t="str">
-        <v>medium</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Wait for the gateway's final processing before asserting (e.g., waitForURL that returns to FoodHub, or waitForResponse on the order API before checking UI); verify gateway health as part of setup</v>
-      </c>
-      <c r="I5" t="str">
-        <v>sample-flaky-log.txt</v>
-      </c>
-      <c r="J5" t="str">
-        <v>DeepSeek</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>FOL-005</v>
-      </c>
-      <c r="B6" t="str">
-        <v>E2E Tests (Playwright)</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Retry signal</v>
-      </c>
-      <c r="D6" t="str">
-        <v>1 occurrence: test 'customer can view menu, pay through the gateway, and receive an AI suggestion' failed with ERR_CONNECTION_REFUSED, then passed on Retry #1</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Environment not ready for initial attempt; retry succeeds only after the app fully starts</v>
-      </c>
-      <c r="F6" t="str">
-        <v>environment</v>
-      </c>
-      <c r="G6" t="str">
-        <v>high</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Remove dependency on retries by ensuring pre-test health checks; if retries are kept, investigate the exact readiness gap and add an explicit wait before the first navigation</v>
-      </c>
-      <c r="I6" t="str">
-        <v>sample-flaky-log.txt</v>
-      </c>
-      <c r="J6" t="str">
-        <v>DeepSeek</v>
+        <v>deepseek-v4-pro high when FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M12"/>
+  <cols>
+    <col min="1" max="1" width="13.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="64.83203125" customWidth="1"/>
+    <col min="5" max="5" width="55.83203125" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" customWidth="1"/>
+    <col min="7" max="7" width="64.83203125" customWidth="1"/>
+    <col min="8" max="8" width="33.83203125" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="7.83203125" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" customWidth="1"/>
+    <col min="13" max="13" width="38.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -648,31 +611,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FH-EDGE-001</v>
+        <v>AI-EDGE-001</v>
       </c>
       <c r="B2" t="str">
         <v>Edge Case</v>
       </c>
       <c r="C2" t="str">
-        <v>API</v>
+        <v>Menu</v>
       </c>
       <c r="D2" t="str">
-        <v>POST /order with negative quantity for a menu item</v>
+        <v>Menu API returns stable item contract</v>
       </c>
       <c r="E2" t="str">
-        <v>Validation might not reject negative integer quantity, leading to incorrect pricing or downstream errors</v>
+        <v>API contract breaking</v>
       </c>
       <c r="F2" t="str">
         <v>Integration</v>
       </c>
       <c r="G2" t="str">
-        <v>Response status 400 with error 'Invalid order'</v>
+        <v>GET /menu returns items with id, name, price, and category</v>
       </c>
       <c r="H2" t="str">
-        <v>Payload with items: [{ menuItemId: 'burger-classic', quantity: -1 }], valid paymentToken and customerName</v>
+        <v>Menu response fixture</v>
       </c>
       <c r="I2" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -681,39 +644,39 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>AI-generated</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v>DeepSeek</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FH-EDGE-002</v>
+        <v>AI-EDGE-002</v>
       </c>
       <c r="B3" t="str">
         <v>Edge Case</v>
       </c>
       <c r="C3" t="str">
-        <v>API</v>
+        <v>Order</v>
       </c>
       <c r="D3" t="str">
-        <v>POST /order with zero quantity for a menu item</v>
+        <v>Order contains an unknown menu item</v>
       </c>
       <c r="E3" t="str">
-        <v>Zero quantity should be rejected per business logic but may pass validation</v>
+        <v>Invalid menu items</v>
       </c>
       <c r="F3" t="str">
         <v>Integration</v>
       </c>
       <c r="G3" t="str">
-        <v>Response status 400 with error 'Invalid order'</v>
+        <v>POST /order returns 400 Invalid order</v>
       </c>
       <c r="H3" t="str">
-        <v>Payload with items: [{ menuItemId: 'burger-classic', quantity: 0 }], valid paymentToken and customerName</v>
+        <v>Unknown item id payload</v>
       </c>
       <c r="I3" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -722,39 +685,39 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>AI-generated</v>
+        <v/>
       </c>
       <c r="M3" t="str">
-        <v>DeepSeek</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FH-EDGE-003</v>
+        <v>AI-EDGE-003</v>
       </c>
       <c r="B4" t="str">
         <v>Edge Case</v>
       </c>
       <c r="C4" t="str">
-        <v>API</v>
+        <v>Order</v>
       </c>
       <c r="D4" t="str">
-        <v>POST /order with non-integer quantity (e.g., 1.5)</v>
+        <v>Order contains no items</v>
       </c>
       <c r="E4" t="str">
-        <v>Zod schema int validation might accept if coerced? Should reject.</v>
+        <v>Invalid empty orders</v>
       </c>
       <c r="F4" t="str">
         <v>Integration</v>
       </c>
       <c r="G4" t="str">
-        <v>Response status 400 with error 'Invalid order'</v>
+        <v>POST /order returns 400 with empty-order detail</v>
       </c>
       <c r="H4" t="str">
-        <v>Payload with items: [{ menuItemId: 'burger-classic', quantity: 1.5 }], valid paymentToken and customerName</v>
+        <v>Empty items payload</v>
       </c>
       <c r="I4" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -763,39 +726,39 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>AI-generated</v>
+        <v/>
       </c>
       <c r="M4" t="str">
-        <v>DeepSeek</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>FH-EDGE-004</v>
+        <v>AI-EDGE-004</v>
       </c>
       <c r="B5" t="str">
         <v>Edge Case</v>
       </c>
       <c r="C5" t="str">
-        <v>API</v>
+        <v>Totals</v>
       </c>
       <c r="D5" t="str">
-        <v>POST /order with quantity exceeding upper boundary (21)</v>
+        <v>Order has mixed item quantities and decimal prices</v>
       </c>
       <c r="E5" t="str">
-        <v>Boundary check at 20 may be missed, leading to order creation with excessive quantity</v>
+        <v>Incorrect totals</v>
       </c>
       <c r="F5" t="str">
-        <v>Integration</v>
+        <v>Unit</v>
       </c>
       <c r="G5" t="str">
-        <v>Response status 400 with error 'Invalid order'</v>
+        <v>Total is rounded to two decimals and payment is charged once</v>
       </c>
       <c r="H5" t="str">
-        <v>Payload with items: [{ menuItemId: 'burger-classic', quantity: 21 }], valid paymentToken and customerName</v>
+        <v>Mixed quantity order builder</v>
       </c>
       <c r="I5" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -804,261 +767,261 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>AI-generated</v>
+        <v/>
       </c>
       <c r="M5" t="str">
-        <v>DeepSeek</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FH-MISS-001</v>
+        <v>AI-EDGE-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Missing Scenario</v>
+        <v>Edge Case</v>
       </c>
       <c r="C6" t="str">
-        <v>UI</v>
+        <v>Invoice</v>
       </c>
       <c r="D6" t="str">
-        <v>Customer sees error message when payment gateway is unreachable</v>
+        <v>Paid order invoice link shows transaction, order, card last 4, paid-via, and customer name</v>
       </c>
       <c r="E6" t="str">
-        <v>User receives no feedback or a generic error when gateway is down, causing confusion</v>
+        <v>Receipt/invoice evidence missing</v>
       </c>
       <c r="F6" t="str">
         <v>E2E</v>
       </c>
       <c r="G6" t="str">
-        <v>Appropriate error message displayed (e.g., 'FoodHub Payment Gateway unavailable'), user can retry</v>
+        <v>Invoice panel opens from last transaction link and matches payment gateway data</v>
       </c>
       <c r="H6" t="str">
-        <v>Start app without payment gateway; use any valid card</v>
+        <v>Approved checkout fixture</v>
       </c>
       <c r="I6" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>Simulate gateway down by stopping port 4174 before checkout</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>AI-generated</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>DeepSeek</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>FH-MISS-002</v>
+        <v>AI-MISS-001</v>
       </c>
       <c r="B7" t="str">
         <v>Missing Scenario</v>
       </c>
       <c r="C7" t="str">
-        <v>Observability</v>
+        <v>Order</v>
       </c>
       <c r="D7" t="str">
-        <v>Verify request logger writes structured log entry for POST /order</v>
+        <v>Duplicate items are submitted as separate order lines</v>
       </c>
       <c r="E7" t="str">
-        <v>Missing observability data for order creation events, hampering debugging</v>
+        <v>Duplicate lines can expose total-calculation mistakes</v>
       </c>
       <c r="F7" t="str">
         <v>Integration</v>
       </c>
       <c r="G7" t="str">
-        <v>Log file contains entry with method POST, path /order, statusCode 201/400/402, durationMs, requestId</v>
+        <v>Submit the same menu item twice and verify totals remain correct</v>
       </c>
       <c r="H7" t="str">
-        <v>Send valid order; check qa-artifacts/observability/raw/request-logs.jsonl</v>
+        <v>Duplicate item order builder</v>
       </c>
       <c r="I7" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>Run test with NODE_ENV not 'test' to enable logger</v>
+        <v/>
       </c>
       <c r="L7" t="str">
-        <v>AI-generated</v>
+        <v/>
       </c>
       <c r="M7" t="str">
-        <v>DeepSeek</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>FH-MISS-003</v>
+        <v>AI-MISS-002</v>
       </c>
       <c r="B8" t="str">
         <v>Missing Scenario</v>
       </c>
       <c r="C8" t="str">
-        <v>Payment</v>
+        <v>Order</v>
       </c>
       <c r="D8" t="str">
-        <v>POST /order with invalid payment token format (e.g., 'invalid')</v>
+        <v>Large order at maximum accepted quantity</v>
       </c>
       <c r="E8" t="str">
-        <v>Payment service may throw unexpected error or not return 402</v>
+        <v>Boundary quantities can break validation or totals</v>
       </c>
       <c r="F8" t="str">
         <v>Integration</v>
       </c>
       <c r="G8" t="str">
-        <v>Response status 402 with error 'Payment failed' and details message</v>
+        <v>Submit quantity 20 and verify the order is accepted with correct total</v>
       </c>
       <c r="H8" t="str">
-        <v>Payload with paymentToken: 'invalid'</v>
+        <v>Boundary quantity order builder</v>
       </c>
       <c r="I8" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>FakePaymentGateway returns failed if token does not start with 'gateway_paid_' or 'tok_success'</v>
+        <v/>
       </c>
       <c r="L8" t="str">
-        <v>AI-generated</v>
+        <v/>
       </c>
       <c r="M8" t="str">
-        <v>DeepSeek</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>FH-MISS-004</v>
+        <v>AI-MISS-003</v>
       </c>
       <c r="B9" t="str">
         <v>Missing Scenario</v>
       </c>
       <c r="C9" t="str">
-        <v>Persistence</v>
+        <v>Order</v>
       </c>
       <c r="D9" t="str">
-        <v>Verify paid order is persisted and retrievable from PostgreSQL via Testcontainers</v>
+        <v>Invalid payload shapes are rejected predictably</v>
       </c>
       <c r="E9" t="str">
-        <v>Order data may not be saved, leading to loss of transaction records</v>
+        <v>Malformed clients should receive predictable errors</v>
       </c>
       <c r="F9" t="str">
-        <v>Integration (Testcontainers)</v>
+        <v>Integration</v>
       </c>
       <c r="G9" t="str">
-        <v>After successful POST /order, query database returns saved receipt with same orderId</v>
+        <v>Submit items as an object instead of an array and verify 400 response</v>
       </c>
       <c r="H9" t="str">
-        <v>Real PostgreSQL container; insert order, then read back</v>
+        <v>Malformed payload fixture</v>
       </c>
       <c r="I9" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>Requires OrderRepository with save method; must be implemented and tested</v>
+        <v/>
       </c>
       <c r="L9" t="str">
-        <v>AI-generated</v>
+        <v/>
       </c>
       <c r="M9" t="str">
-        <v>DeepSeek</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>FH-EXPN-001</v>
+        <v>AI-COV-001</v>
       </c>
       <c r="B10" t="str">
         <v>Coverage Expansion</v>
       </c>
       <c r="C10" t="str">
-        <v>API</v>
+        <v>Payment</v>
       </c>
       <c r="D10" t="str">
-        <v>POST /order with all available menu items in a single order</v>
+        <v>Gateway cancellation should not create paid orders</v>
       </c>
       <c r="E10" t="str">
-        <v>Total calculation may overflow or misbehave with many line items</v>
+        <v>Cancelled payments must not create orders</v>
       </c>
       <c r="F10" t="str">
-        <v>Integration</v>
+        <v>E2E</v>
       </c>
       <c r="G10" t="str">
-        <v>Status 201 with correct total sum of all items prices times quantities (each quantity 1)</v>
+        <v>Cancel gateway flow and verify no order is created</v>
       </c>
       <c r="H10" t="str">
-        <v>Payload with items array containing every menu item id with quantity 1</v>
+        <v>Cancelled checkout fixture</v>
       </c>
       <c r="I10" t="str">
-        <v>To Do</v>
+        <v>Candidate</v>
       </c>
       <c r="J10" t="str">
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>Ensures pricing logic handles full menu</v>
+        <v/>
       </c>
       <c r="L10" t="str">
-        <v>AI-generated</v>
+        <v/>
       </c>
       <c r="M10" t="str">
-        <v>DeepSeek</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>FH-EXPN-002</v>
+        <v>AI-COV-002</v>
       </c>
       <c r="B11" t="str">
         <v>Coverage Expansion</v>
       </c>
       <c r="C11" t="str">
-        <v>Visual</v>
+        <v>Observability</v>
       </c>
       <c r="D11" t="str">
-        <v>Visual regression test on mobile viewport (iPhone 12)</v>
+        <v>Dashboard refresh and truncate controls have script-level verification</v>
       </c>
       <c r="E11" t="str">
-        <v>UI may break on smaller screens, text overflow, layout shift</v>
+        <v>Observability drift</v>
       </c>
       <c r="F11" t="str">
-        <v>E2E (Playwright)</v>
+        <v>Report</v>
       </c>
       <c r="G11" t="str">
-        <v>Screenshots match baseline for menu, cart, and gateway states on mobile</v>
+        <v>Refresh Firebase-backed dashboard and verify generated workbook sheets</v>
       </c>
       <c r="H11" t="str">
-        <v>Use Playwright device emulation for iPhone 12</v>
+        <v>Observability metrics fixture</v>
       </c>
       <c r="I11" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>Add new snapshot files for mobile</v>
+        <v/>
       </c>
       <c r="L11" t="str">
-        <v>AI-generated</v>
+        <v/>
       </c>
       <c r="M11" t="str">
-        <v>DeepSeek</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>FH-EXPN-003</v>
+        <v>AI-COV-003</v>
       </c>
       <c r="B12" t="str">
         <v>Coverage Expansion</v>
@@ -1067,210 +1030,59 @@
         <v>Load</v>
       </c>
       <c r="D12" t="str">
-        <v>Load test with 50 concurrent virtual users creating orders</v>
+        <v>API handles repeated browse-and-order traffic</v>
       </c>
       <c r="E12" t="str">
-        <v>System may exceed p95 latency or failure thresholds under high concurrency</v>
+        <v>Performance regression</v>
       </c>
       <c r="F12" t="str">
-        <v>Load (k6)</v>
+        <v>Load</v>
       </c>
       <c r="G12" t="str">
-        <v>http_req_failed rate &lt; 0.05, p95 latency &lt; 500ms, foodhub_order_failures rate &lt; 0.02</v>
+        <v>k6 thresholds pass for p95 latency, HTTP failures, and paid-order failures</v>
       </c>
       <c r="H12" t="str">
-        <v>Set VUS=50, ramp-up 30s, steady 60s; use random order templates</v>
+        <v>k6 seeded load data</v>
       </c>
       <c r="I12" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>Run after ensuring API and gateway are on HOST=0.0.0.0</v>
+        <v/>
       </c>
       <c r="L12" t="str">
-        <v>AI-generated</v>
+        <v/>
       </c>
       <c r="M12" t="str">
-        <v>DeepSeek</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>FH-EXPN-004</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Coverage Expansion</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Contract</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Pact contract test verifying consumer (Web UI) can consume provider (API) endpoints correctly</v>
-      </c>
-      <c r="E13" t="str">
-        <v>API contract regressions not detected during CI if only integration tests run</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Contract (Pact)</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Pact verification passes for all interactions defined in consumer tests</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Define Pact interactions for menu and order endpoints; provider state setup</v>
-      </c>
-      <c r="I13" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v>Implementation detail: use @pact-foundation/pact</v>
-      </c>
-      <c r="L13" t="str">
-        <v>AI-generated</v>
-      </c>
-      <c r="M13" t="str">
-        <v>DeepSeek</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>FH-EXPN-005</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Coverage Expansion</v>
-      </c>
-      <c r="C14" t="str">
-        <v>AI Recommendation</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Verify aiSuggestion is empty or defaults when cart is empty or consists only of drinks</v>
-      </c>
-      <c r="E14" t="str">
-        <v>AI suggestion logic may generate weird recommendations for edge cases</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Unit/Integration</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Recommended string is sensible and not empty for standard orders; for empty cart or drinks-only, suggestion may be absent or generic</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Order with only drink items (e.g., cola-zero, lemonade)</v>
-      </c>
-      <c r="I14" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v>Check recommendationService logic in src/services/recommendationService.ts</v>
-      </c>
-      <c r="L14" t="str">
-        <v>AI-generated</v>
-      </c>
-      <c r="M14" t="str">
-        <v>DeepSeek</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>FH-EXPN-006</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Coverage Expansion</v>
-      </c>
-      <c r="C15" t="str">
-        <v>UI</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Checkout button disabled state when cart is empty</v>
-      </c>
-      <c r="E15" t="str">
-        <v>User may be able to click checkout with empty cart if button enabled incorrectly</v>
-      </c>
-      <c r="F15" t="str">
-        <v>E2E</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Checkout button should be disabled and have aria-disabled attribute</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Navigate to page with empty cart</v>
-      </c>
-      <c r="I15" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v>Use expect(page.locator('#checkout-button')).toBeDisabled()</v>
-      </c>
-      <c r="L15" t="str">
-        <v>AI-generated</v>
-      </c>
-      <c r="M15" t="str">
-        <v>DeepSeek</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>FH-MISS-005</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Missing Scenario</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Invoice</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Invoice link not available after page refresh mid-session</v>
-      </c>
-      <c r="E16" t="str">
-        <v>User loses ability to view invoice after browser refresh since state is stored in memory only</v>
-      </c>
-      <c r="F16" t="str">
-        <v>E2E</v>
-      </c>
-      <c r="G16" t="str">
-        <v>After refresh, invoice link panel should be hidden (no invoice state persisted); user may need to re-order to see invoice</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Complete an order, then refresh the page; verify invoice link not present</v>
-      </c>
-      <c r="I16" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v>Not a bug but a UX gap; consider persisting last invoice in localStorage</v>
-      </c>
-      <c r="L16" t="str">
-        <v>AI-generated</v>
-      </c>
-      <c r="M16" t="str">
-        <v>DeepSeek</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K7"/>
+  <cols>
+    <col min="1" max="1" width="13.83203125" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="39.83203125" customWidth="1"/>
+    <col min="6" max="6" width="43.83203125" customWidth="1"/>
+    <col min="7" max="7" width="56.83203125" customWidth="1"/>
+    <col min="8" max="8" width="34.83203125" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="38.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1309,392 +1121,217 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TD-001</v>
+        <v>AI-DATA-001</v>
       </c>
       <c r="B2" t="str">
-        <v>EDGE-001</v>
+        <v>AI-EDGE-004</v>
       </c>
       <c r="C2" t="str">
         <v>Edge Case</v>
       </c>
       <c r="D2" t="str">
-        <v>Order payload</v>
+        <v>Randomized mixed order</v>
       </c>
       <c r="E2" t="str">
-        <v>createOrder with quantity 1</v>
+        <v>createRandomOrder(seed)</v>
       </c>
       <c r="F2" t="str">
-        <v>{"items":[{"menuItemId":"burger-classic","quantity":1}],"paymentToken":"gateway_paid_test123","customerName":"Test"}</v>
+        <v>Seeded deterministic mixed menu items</v>
       </c>
       <c r="G2" t="str">
-        <v>Verify that the minimum valid quantity (1) is accepted and correctly priced</v>
+        <v>Broaden order combinations without shared mutable data</v>
       </c>
       <c r="H2" t="str">
-        <v>Integration test</v>
+        <v>Mixed-quantity total validation</v>
       </c>
       <c r="I2" t="str">
-        <v>suggested</v>
+        <v>Implemented</v>
       </c>
       <c r="J2" t="str">
-        <v>Manual analysis</v>
+        <v/>
       </c>
       <c r="K2" t="str">
-        <v>N/A</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TD-002</v>
+        <v>AI-DATA-002</v>
       </c>
       <c r="B3" t="str">
-        <v>EDGE-002</v>
+        <v>AI-MISS-002</v>
       </c>
       <c r="C3" t="str">
-        <v>Edge Case</v>
+        <v>Missing Scenario</v>
       </c>
       <c r="D3" t="str">
-        <v>Order payload</v>
+        <v>Boundary quantity</v>
       </c>
       <c r="E3" t="str">
-        <v>createBoundaryQuantityOrder(20) (already exists)</v>
+        <v>createBoundaryQuantityOrder(20)</v>
       </c>
       <c r="F3" t="str">
-        <v>{"items":[{"menuItemId":"burger-classic","quantity":20}],"paymentToken":"gateway_paid_test456","customerName":"Boundary"}</v>
+        <v>burger-classic x 20</v>
       </c>
       <c r="G3" t="str">
-        <v>Confirm boundary quantity 20 is accepted and total is correct (already covered by existing test, listed for completeness)</v>
+        <v>Validate upper accepted quantity</v>
       </c>
       <c r="H3" t="str">
-        <v>Integration test</v>
+        <v>Large order missing scenario</v>
       </c>
       <c r="I3" t="str">
-        <v>covered</v>
+        <v>Implemented</v>
       </c>
       <c r="J3" t="str">
-        <v>Existing test</v>
+        <v/>
       </c>
       <c r="K3" t="str">
-        <v>N/A</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TD-003</v>
+        <v>AI-DATA-003</v>
       </c>
       <c r="B4" t="str">
-        <v>MISS-001</v>
+        <v>AI-MISS-001</v>
       </c>
       <c r="C4" t="str">
         <v>Missing Scenario</v>
       </c>
       <c r="D4" t="str">
-        <v>Payment token</v>
+        <v>Duplicate item lines</v>
       </c>
       <c r="E4" t="str">
-        <v>createOrder with paymentToken "tok_success"</v>
+        <v>createDuplicateItemOrder()</v>
       </c>
       <c r="F4" t="str">
-        <v>{"items":[{"menuItemId":"lemonade","quantity":2}],"paymentToken":"tok_success","customerName":"TokenSuccess"}</v>
+        <v>burger-classic x 1 and burger-classic x 2</v>
       </c>
       <c r="G4" t="str">
-        <v>Test that the legacy success token 'tok_success' is handled correctly and returns a paid receipt</v>
+        <v>Validate totals across repeated menu item ids</v>
       </c>
       <c r="H4" t="str">
-        <v>Integration test</v>
+        <v>Duplicate items missing scenario</v>
       </c>
       <c r="I4" t="str">
-        <v>suggested</v>
+        <v>Implemented</v>
       </c>
       <c r="J4" t="str">
-        <v>Code review – paymentService accepts 'tok_success' but no integration test uses it</v>
+        <v/>
       </c>
       <c r="K4" t="str">
-        <v>N/A</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TD-004</v>
+        <v>AI-DATA-004</v>
       </c>
       <c r="B5" t="str">
-        <v>MISS-002</v>
+        <v>AI-EDGE-005</v>
       </c>
       <c r="C5" t="str">
-        <v>Missing Scenario</v>
+        <v>Edge Case</v>
       </c>
       <c r="D5" t="str">
-        <v>Order payload</v>
+        <v>Invoice customer</v>
       </c>
       <c r="E5" t="str">
-        <v>createOrder with customerName set to whitespace-only string</v>
+        <v>createApprovedCheckout().customerName</v>
       </c>
       <c r="F5" t="str">
-        <v>{"items":[{"menuItemId":"wrap-veggie","quantity":1}],"paymentToken":"gateway_paid_test789","customerName":"   "}</v>
+        <v>FoodHub Demo User</v>
       </c>
       <c r="G5" t="str">
-        <v>Ensure that a customerName consisting only of whitespace is rejected (Zod .trim().min(1))</v>
+        <v>Verify invoice customer-name publishing</v>
       </c>
       <c r="H5" t="str">
-        <v>Integration test</v>
+        <v>Invoice receipt validation</v>
       </c>
       <c r="I5" t="str">
-        <v>suggested</v>
+        <v>Implemented</v>
       </c>
       <c r="J5" t="str">
-        <v>Code analysis – schema uses .trim().min(1) but not tested</v>
+        <v/>
       </c>
       <c r="K5" t="str">
-        <v>N/A</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TD-005</v>
+        <v>AI-DATA-005</v>
       </c>
       <c r="B6" t="str">
-        <v>EDGE-003</v>
+        <v>AI-COV-003</v>
       </c>
       <c r="C6" t="str">
-        <v>Edge Case</v>
+        <v>Coverage Expansion</v>
       </c>
       <c r="D6" t="str">
-        <v>Order payload</v>
+        <v>Load traffic</v>
       </c>
       <c r="E6" t="str">
-        <v>createOrder with quantity 0</v>
+        <v>k6 __VU/__ITER payment token</v>
       </c>
       <c r="F6" t="str">
-        <v>{"items":[{"menuItemId":"burger-classic","quantity":0}],"paymentToken":"gateway_paid_test000","customerName":"ZeroQty"}</v>
+        <v>gateway_paid_load_1_1</v>
       </c>
       <c r="G6" t="str">
-        <v>Verify that quantity 0 is rejected (z.number().int().positive())</v>
+        <v>Avoid payment-token collisions during load execution</v>
       </c>
       <c r="H6" t="str">
-        <v>Integration test</v>
+        <v>Load coverage expansion</v>
       </c>
       <c r="I6" t="str">
-        <v>suggested</v>
+        <v>Implemented</v>
       </c>
       <c r="J6" t="str">
-        <v>Manual analysis – positive constraint not covered</v>
+        <v/>
       </c>
       <c r="K6" t="str">
-        <v>N/A</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TD-006</v>
+        <v>AI-DATA-006</v>
       </c>
       <c r="B7" t="str">
-        <v>EDGE-004</v>
+        <v>AI-COV-002</v>
       </c>
       <c r="C7" t="str">
-        <v>Edge Case</v>
+        <v>Coverage Expansion</v>
       </c>
       <c r="D7" t="str">
-        <v>Order payload</v>
+        <v>Observability metrics</v>
       </c>
       <c r="E7" t="str">
-        <v>createOrder with negative quantity</v>
+        <v>latest-observability-metrics.json</v>
       </c>
       <c r="F7" t="str">
-        <v>{"items":[{"menuItemId":"cola-zero","quantity":-3}],"paymentToken":"gateway_paid_test111","customerName":"NegativeQty"}</v>
+        <v>requestCount, errorCount, p95DurationMs</v>
       </c>
       <c r="G7" t="str">
-        <v>Ensure negative quantity is rejected by Zod or validation logic</v>
+        <v>Feed Firebase and charted dashboard</v>
       </c>
       <c r="H7" t="str">
-        <v>Integration test</v>
+        <v>Observability coverage expansion</v>
       </c>
       <c r="I7" t="str">
-        <v>suggested</v>
+        <v>Implemented</v>
       </c>
       <c r="J7" t="str">
-        <v>Manual analysis – negative integer not tested</v>
+        <v/>
       </c>
       <c r="K7" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>TD-007</v>
-      </c>
-      <c r="B8" t="str">
-        <v>MISS-003</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Missing Scenario</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Order payload</v>
-      </c>
-      <c r="E8" t="str">
-        <v>createOrder with null items element</v>
-      </c>
-      <c r="F8" t="str">
-        <v>{"items":[null],"paymentToken":"gateway_paid_test222","customerName":"NullItem"}</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Check that an array containing null is rejected with 400 error</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Integration test</v>
-      </c>
-      <c r="I8" t="str">
-        <v>suggested</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Code review – Zod array of objects, null element not tested</v>
-      </c>
-      <c r="K8" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>TD-008</v>
-      </c>
-      <c r="B9" t="str">
-        <v>COV-001</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Coverage Expansion</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Order payload</v>
-      </c>
-      <c r="E9" t="str">
-        <v>createRandomOrder(10) or a new builder createLargeDistinctOrder</v>
-      </c>
-      <c r="F9" t="str">
-        <v>{"items":[{"menuItemId":"burger-classic","quantity":1},{"menuItemId":"wrap-veggie","quantity":2},{"menuItemId":"lemonade","quantity":1},{"menuItemId":"cola-zero","quantity":1},{"menuItemId":"fries-large","quantity":1}],"paymentToken":"gateway_paid_test333","customerName":"LargeOrder"}</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Verify that an order with many unique items (e.g., 5+ distinct menu items) processes correctly and total is accurate</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Integration test / Load test</v>
-      </c>
-      <c r="I9" t="str">
-        <v>suggested</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Coverage analysis – only small orders tested</v>
-      </c>
-      <c r="K9" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>TD-009</v>
-      </c>
-      <c r="B10" t="str">
-        <v>COV-002</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Coverage Expansion</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Order payload</v>
-      </c>
-      <c r="E10" t="str">
-        <v>createOrder with a price that causes floating point rounding</v>
-      </c>
-      <c r="F10" t="str">
-        <v>{"items":[{"menuItemId":"items with price 0.10","quantity":3}],"paymentToken":"gateway_paid_test444","customerName":"RoundingTest"}</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Ensure roundMoney correctly handles floating point arithmetic (e.g., 0.10 * 3 = 0.30, not 0.30000000000000004)</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Integration test</v>
-      </c>
-      <c r="I10" t="str">
-        <v>suggested</v>
-      </c>
-      <c r="J10" t="str">
-        <v>Code analysis – roundMoney uses Number.EPSILON, no explicit test</v>
-      </c>
-      <c r="K10" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>TD-010</v>
-      </c>
-      <c r="B11" t="str">
-        <v>MISS-004</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Missing Scenario</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Payment token</v>
-      </c>
-      <c r="E11" t="str">
-        <v>createOrder with paymentToken missing from request</v>
-      </c>
-      <c r="F11" t="str">
-        <v>{"items":[{"menuItemId":"fries-large","quantity":1}],"customerName":"NoToken"}</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Validate that a missing paymentToken field is caught by Zod (z.string().min(1)) and returns 400</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Integration test</v>
-      </c>
-      <c r="I11" t="str">
-        <v>suggested</v>
-      </c>
-      <c r="J11" t="str">
-        <v>Manual analysis – required field not tested for absence</v>
-      </c>
-      <c r="K11" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>TD-011</v>
-      </c>
-      <c r="B12" t="str">
-        <v>EDGE-005</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Edge Case</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Order payload</v>
-      </c>
-      <c r="E12" t="str">
-        <v>createOrder with customerName of length 255</v>
-      </c>
-      <c r="F12" t="str">
-        <v>{"items":[{"menuItemId":"burger-classic","quantity":1}],"paymentToken":"gateway_paid_test555","customerName":"a... (255 characters)"}</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Test that a very long customerName (255 chars) is accepted or rejected appropriately (no length constraint in schema, but may cause DB issues)</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Integration test</v>
-      </c>
-      <c r="I12" t="str">
-        <v>suggested</v>
-      </c>
-      <c r="J12" t="str">
-        <v>Edge case analysis – no length validation on customerName</v>
-      </c>
-      <c r="K12" t="str">
-        <v>N/A</v>
+        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1703,9 +1340,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="90.83203125" customWidth="1"/>
+    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="47.83203125" customWidth="1"/>
+    <col min="3" max="3" width="64.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1735,7 +1372,7 @@
         <v>DeepSeek API key</v>
       </c>
       <c r="B3" t="str">
-        <v>Configured</v>
+        <v>Not configured</v>
       </c>
       <c r="C3" t="str">
         <v>DeepSeek bearer token loaded from Firestore foodhub-6ba1c/deepSeek/ooz80WHRgmUV3WseQDnF/api-key</v>

--- a/qa-artifacts/FoodHub-AI-Test-Analysis.xlsx
+++ b/qa-artifacts/FoodHub-AI-Test-Analysis.xlsx
@@ -400,19 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
-  <cols>
-    <col min="1" max="1" width="13.83203125" customWidth="1"/>
-    <col min="2" max="2" width="27.83203125" customWidth="1"/>
-    <col min="3" max="3" width="64.83203125" customWidth="1"/>
-    <col min="4" max="4" width="49.83203125" customWidth="1"/>
-    <col min="5" max="5" width="53.83203125" customWidth="1"/>
-    <col min="6" max="6" width="31.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="58.83203125" customWidth="1"/>
-    <col min="9" max="9" width="43.83203125" customWidth="1"/>
-    <col min="10" max="10" width="48.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:J9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -448,125 +436,270 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AI-FAIL-001</v>
+        <v>F-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Log capture</v>
+        <v>Network/Service Startup</v>
       </c>
       <c r="C2" t="str">
-        <v>Vitest, Pact, Playwright, Testcontainers, k6, and viewer logs retained</v>
+        <v>ERR_CONNECTION_REFUSED on page.goto</v>
       </c>
       <c r="D2" t="str">
-        <v>Test logs and generated reports</v>
+        <v>Error: page.goto: net::ERR_CONNECTION_REFUSED at http://127.0.0.1:4173/</v>
       </c>
       <c r="E2" t="str">
-        <v>Unknown until logs are analyzed</v>
+        <v>The FoodHub web application was not running on port 4173 when the E2E test attempted to navigate.</v>
       </c>
       <c r="F2" t="str">
-        <v>Unknown</v>
+        <v>Environment</v>
       </c>
       <c r="G2" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="H2" t="str">
-        <v>Run analyzer and compare against observability artifacts</v>
+        <v>Ensure the app server is started before E2E tests, e.g., via Playwright's webServer config or explicit health-check wait.</v>
       </c>
       <c r="I2" t="str">
-        <v>Local fallback</v>
+        <v>sample-flaky-log.txt</v>
       </c>
       <c r="J2" t="str">
-        <v>deepseek-v4-pro high when FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AI-FAIL-002</v>
+        <v>F-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Pattern analysis</v>
+        <v>Payment Gateway Flow</v>
       </c>
       <c r="C3" t="str">
-        <v>Timeout, selector, startup, Pact, DB, and k6 signals scanned</v>
+        <v>Timeout waiting for declined payment message</v>
       </c>
       <c r="D3" t="str">
-        <v>tests/fixtures/failureLogs/sample-flaky-log.txt</v>
+        <v>Locator('#gateway-message') timed out after 5000ms. Expected: 'Payment declined for xxxx-xxxx-xxxx-8911.' Received: 'Processing through FoodHub Payment Gateway...'</v>
       </c>
       <c r="E3" t="str">
-        <v>Potential flaky test or environment issue</v>
+        <v>The payment gateway UI wasn't updated to the final declined state within the assertion timeout, possibly due to async redirect processing or a slower gateway response.</v>
       </c>
       <c r="F3" t="str">
-        <v>Test or Environment</v>
+        <v>Test Bug</v>
       </c>
       <c r="G3" t="str">
         <v>Medium</v>
       </c>
       <c r="H3" t="str">
-        <v>Classify each hit and attach next diagnostic command</v>
+        <v>Increase the Playwright timeout for this assertion or use a web-first assertion that waits for the final text to appear rather than a fixed text.</v>
       </c>
       <c r="I3" t="str">
-        <v>Local fallback</v>
+        <v>sample-flaky-log.txt</v>
       </c>
       <c r="J3" t="str">
-        <v>deepseek-v4-pro high when FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AI-FAIL-003</v>
+        <v>F-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Observability correlation</v>
+        <v>Selector/UI Locator</v>
       </c>
       <c r="C4" t="str">
-        <v>Failure details compared with Firebase run history and request logs</v>
+        <v>Brittle locators causing test failures (3 hits)</v>
       </c>
       <c r="D4" t="str">
-        <v>FoodHub-Observability-Dashboard.xlsx</v>
+        <v>Failure analysis report indicates 3 hits of selector/UI locator issues in the log.</v>
       </c>
       <c r="E4" t="str">
-        <v>Request-level regression or missing metric evidence</v>
+        <v>UI elements changed between test runs (e.g., text content, IDs, or structure) causing locator mismatches.</v>
       </c>
       <c r="F4" t="str">
-        <v>Product, Test, or Environment</v>
+        <v>Test Bug</v>
       </c>
       <c r="G4" t="str">
         <v>Medium</v>
       </c>
       <c r="H4" t="str">
-        <v>Correlate failed test timestamp with request logs</v>
+        <v>Replace CSS-only selectors with role-based locators (e.g., getByRole) or stable data-testid attributes.</v>
       </c>
       <c r="I4" t="str">
-        <v>deepseek-v4-pro when live mode is enabled</v>
+        <v>failure-analysis-report.md</v>
       </c>
       <c r="J4" t="str">
-        <v>deepseek-v4-pro high when FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>F-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Timeout</v>
+      </c>
+      <c r="C5" t="str">
+        <v>General timeout on locator assertion (2 hits)</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Failure analysis report notes 2 timeout hits; one example from F-002.</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Async operations or navigation took longer than the configured timeout, possibly due to slow environment or resource contention.</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Test Bug</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Increase timeouts for flaky assertions and use waitForLoadState to confirm page readiness.</v>
+      </c>
+      <c r="I5" t="str">
+        <v>failure-analysis-report.md</v>
+      </c>
+      <c r="J5" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>F-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Retry/Flakiness</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Test passed after retry indicating flaky environment</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Log shows 'Retry #1 ok' immediately after the connection refused error.</v>
+      </c>
+      <c r="E6" t="str">
+        <v>The server became available by the time Playwright retried the test, indicating a startup race condition.</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Environment</v>
+      </c>
+      <c r="G6" t="str">
+        <v>High</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Implement explicit service readiness probes (e.g., retry until /health returns 200) before launching tests.</v>
+      </c>
+      <c r="I6" t="str">
+        <v>sample-flaky-log.txt</v>
+      </c>
+      <c r="J6" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>F-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>k6 Load Test</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Potential threshold breach (p95 latency or failure rate)</v>
+      </c>
+      <c r="D7" t="str">
+        <v>k6 test configuration sets thresholds: http_req_duration p95&lt;500, foodhub_order_failures rate&lt;0.02. No explicit breach in the provided logs.</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Under high load, the server may exceed response time limits or start failing order requests due to payment gateway bottlenecks.</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Low</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Profile endpoints, optimize database queries, or add caching. Adjust thresholds if they are too strict.</v>
+      </c>
+      <c r="I7" t="str">
+        <v>tests/load/foodhub-api.k6.js</v>
+      </c>
+      <c r="J7" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>F-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Docker/Testcontainers</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Testcontainers integration test failure (inferred)</v>
+      </c>
+      <c r="D8" t="str">
+        <v>No direct log entry; inferred from README description of Testcontainers integration tests with PostgreSQL.</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Docker daemon not running, image pull failure, or container startup timeout in CI.</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Environment</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Low</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Ensure Docker is available in the CI environment and configure health checks for the containerized database.</v>
+      </c>
+      <c r="I8" t="str">
+        <v>README.md</v>
+      </c>
+      <c r="J8" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>F-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Report Generation</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Test report or Playwright report missing/corrupt (inferred)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>No explicit entry in log; potential issue based on project's report artifacts.</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Missing directory write permissions, script error during report generation, or report path mismatch.</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Environment</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Low</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Validate that qa-artifacts directory exists and is writable; run report generation script in isolation to check for errors.</v>
+      </c>
+      <c r="I9" t="str">
+        <v>README.md</v>
+      </c>
+      <c r="J9" t="str">
+        <v>DeepSeek</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
-  <cols>
-    <col min="1" max="1" width="13.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="64.83203125" customWidth="1"/>
-    <col min="5" max="5" width="55.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
-    <col min="7" max="7" width="64.83203125" customWidth="1"/>
-    <col min="8" max="8" width="33.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="7.83203125" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" customWidth="1"/>
-    <col min="13" max="13" width="38.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:M26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -611,335 +744,335 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AI-EDGE-001</v>
+        <v>FH-TC-001</v>
       </c>
       <c r="B2" t="str">
         <v>Edge Case</v>
       </c>
       <c r="C2" t="str">
-        <v>Menu</v>
+        <v>API</v>
       </c>
       <c r="D2" t="str">
-        <v>Menu API returns stable item contract</v>
+        <v>POST /order with zero quantity for an item</v>
       </c>
       <c r="E2" t="str">
-        <v>API contract breaking</v>
+        <v>Incorrect total calculation or validation bypass</v>
       </c>
       <c r="F2" t="str">
         <v>Integration</v>
       </c>
       <c r="G2" t="str">
-        <v>GET /menu returns items with id, name, price, and category</v>
+        <v>400 error with message 'Quantity must be an integer between 1 and 20'</v>
       </c>
       <c r="H2" t="str">
-        <v>Menu response fixture</v>
+        <v>Order with quantity=0 for a valid menu item</v>
       </c>
       <c r="I2" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>Code validation in orderService.ts</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>Not currently covered in integration tests</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>code analysis</v>
       </c>
       <c r="M2" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AI-EDGE-002</v>
+        <v>FH-TC-002</v>
       </c>
       <c r="B3" t="str">
         <v>Edge Case</v>
       </c>
       <c r="C3" t="str">
-        <v>Order</v>
+        <v>API</v>
       </c>
       <c r="D3" t="str">
-        <v>Order contains an unknown menu item</v>
+        <v>POST /order with quantity exceeding 20</v>
       </c>
       <c r="E3" t="str">
-        <v>Invalid menu items</v>
+        <v>Validation bypass leading to unexpected behavior or overflow</v>
       </c>
       <c r="F3" t="str">
         <v>Integration</v>
       </c>
       <c r="G3" t="str">
-        <v>POST /order returns 400 Invalid order</v>
+        <v>400 error with message 'Quantity must be an integer between 1 and 20'</v>
       </c>
       <c r="H3" t="str">
-        <v>Unknown item id payload</v>
+        <v>Order with quantity=21 for a valid menu item</v>
       </c>
       <c r="I3" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>Code validation in orderService.ts (line check: quantity &gt; 20)</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>Boundary condition not in current test suite</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>code analysis</v>
       </c>
       <c r="M3" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AI-EDGE-003</v>
+        <v>FH-TC-003</v>
       </c>
       <c r="B4" t="str">
         <v>Edge Case</v>
       </c>
       <c r="C4" t="str">
-        <v>Order</v>
+        <v>API</v>
       </c>
       <c r="D4" t="str">
-        <v>Order contains no items</v>
+        <v>POST /order with negative quantity</v>
       </c>
       <c r="E4" t="str">
-        <v>Invalid empty orders</v>
+        <v>Validation bypass leading to negative total or incorrect state</v>
       </c>
       <c r="F4" t="str">
         <v>Integration</v>
       </c>
       <c r="G4" t="str">
-        <v>POST /order returns 400 with empty-order detail</v>
+        <v>400 error with message 'Quantity must be an integer between 1 and 20'</v>
       </c>
       <c r="H4" t="str">
-        <v>Empty items payload</v>
+        <v>Order with quantity=-1</v>
       </c>
       <c r="I4" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>Code validation in orderService.ts (quantity &lt; 1)</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>Edge case not covered</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>code analysis</v>
       </c>
       <c r="M4" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AI-EDGE-004</v>
+        <v>FH-TC-004</v>
       </c>
       <c r="B5" t="str">
-        <v>Edge Case</v>
+        <v>Missing Scenario</v>
       </c>
       <c r="C5" t="str">
-        <v>Totals</v>
+        <v>API</v>
       </c>
       <c r="D5" t="str">
-        <v>Order has mixed item quantities and decimal prices</v>
+        <v>POST /order with duplicate items but different quantities</v>
       </c>
       <c r="E5" t="str">
-        <v>Incorrect totals</v>
+        <v>Incorrect total calculation or duplicate line handling</v>
       </c>
       <c r="F5" t="str">
-        <v>Unit</v>
+        <v>Integration</v>
       </c>
       <c r="G5" t="str">
-        <v>Total is rounded to two decimals and payment is charged once</v>
+        <v>201 receipt with aggregated line items and correct total</v>
       </c>
       <c r="H5" t="str">
-        <v>Mixed quantity order builder</v>
+        <v>Order with two identical menuItemId with different quantities</v>
       </c>
       <c r="I5" t="str">
-        <v>Implemented</v>
+        <v>Included</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>Test duplicate item lines in api.test.ts (createDuplicateItemOrder)</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>Already implemented as AI missing scenario</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>knowledge base</v>
       </c>
       <c r="M5" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AI-EDGE-005</v>
+        <v>FH-TC-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Edge Case</v>
+        <v>Missing Scenario</v>
       </c>
       <c r="C6" t="str">
-        <v>Invoice</v>
+        <v>API</v>
       </c>
       <c r="D6" t="str">
-        <v>Paid order invoice link shows transaction, order, card last 4, paid-via, and customer name</v>
+        <v>POST /order with large order (boundary quantity 20 for one item)</v>
       </c>
       <c r="E6" t="str">
-        <v>Receipt/invoice evidence missing</v>
+        <v>Performance issues or incorrect total at scale</v>
       </c>
       <c r="F6" t="str">
-        <v>E2E</v>
+        <v>Integration</v>
       </c>
       <c r="G6" t="str">
-        <v>Invoice panel opens from last transaction link and matches payment gateway data</v>
+        <v>201 receipt with total = 20 * item price</v>
       </c>
       <c r="H6" t="str">
-        <v>Approved checkout fixture</v>
+        <v>Order with quantity=20 for a single item (price 9.50 -&gt; total 190)</v>
       </c>
       <c r="I6" t="str">
-        <v>Implemented</v>
+        <v>Included</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>Test createBoundaryQuantityOrder(20) in api.test.ts</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>Already implemented as AI missing scenario</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>knowledge base</v>
       </c>
       <c r="M6" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>AI-MISS-001</v>
+        <v>FH-TC-006</v>
       </c>
       <c r="B7" t="str">
         <v>Missing Scenario</v>
       </c>
       <c r="C7" t="str">
-        <v>Order</v>
+        <v>API</v>
       </c>
       <c r="D7" t="str">
-        <v>Duplicate items are submitted as separate order lines</v>
+        <v>POST /order with invalid payload shape (items as object instead of array)</v>
       </c>
       <c r="E7" t="str">
-        <v>Duplicate lines can expose total-calculation mistakes</v>
+        <v>Zod schema validation not catching structural errors</v>
       </c>
       <c r="F7" t="str">
         <v>Integration</v>
       </c>
       <c r="G7" t="str">
-        <v>Submit the same menu item twice and verify totals remain correct</v>
+        <v>400 error with details</v>
       </c>
       <c r="H7" t="str">
-        <v>Duplicate item order builder</v>
+        <v>Payload with items as object { menuItemId: 'burger-classic', quantity: 1 }</v>
       </c>
       <c r="I7" t="str">
-        <v>Implemented</v>
+        <v>Included</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>Test in api.test.ts for invalid payload shapes</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>Already implemented as AI missing scenario</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>code analysis</v>
       </c>
       <c r="M7" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>AI-MISS-002</v>
+        <v>FH-TC-007</v>
       </c>
       <c r="B8" t="str">
-        <v>Missing Scenario</v>
+        <v>Coverage Expansion</v>
       </c>
       <c r="C8" t="str">
-        <v>Order</v>
+        <v>API</v>
       </c>
       <c r="D8" t="str">
-        <v>Large order at maximum accepted quantity</v>
+        <v>POST /order with missing customerName</v>
       </c>
       <c r="E8" t="str">
-        <v>Boundary quantities can break validation or totals</v>
+        <v>Order created without customer name leading to data inconsistency</v>
       </c>
       <c r="F8" t="str">
         <v>Integration</v>
       </c>
       <c r="G8" t="str">
-        <v>Submit quantity 20 and verify the order is accepted with correct total</v>
+        <v>400 error (Zod validation failure)</v>
       </c>
       <c r="H8" t="str">
-        <v>Boundary quantity order builder</v>
+        <v>Valid payment token and items, but no customerName field</v>
       </c>
       <c r="I8" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>orderSchema requires customerName</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>Not tested; customerName is optional in some contexts? Actually it's required in orderSchema? Need to check - from UI it's required. Integration test missing.</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>requirements</v>
       </c>
       <c r="M8" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>AI-MISS-003</v>
+        <v>FH-TC-008</v>
       </c>
       <c r="B9" t="str">
-        <v>Missing Scenario</v>
+        <v>Coverage Expansion</v>
       </c>
       <c r="C9" t="str">
-        <v>Order</v>
+        <v>UI</v>
       </c>
       <c r="D9" t="str">
-        <v>Invalid payload shapes are rejected predictably</v>
+        <v>Visual regression for invoice preview panel</v>
       </c>
       <c r="E9" t="str">
-        <v>Malformed clients should receive predictable errors</v>
+        <v>UI changes could break invoice display</v>
       </c>
       <c r="F9" t="str">
-        <v>Integration</v>
+        <v>E2E</v>
       </c>
       <c r="G9" t="str">
-        <v>Submit items as an object instead of an array and verify 400 response</v>
+        <v>Screenshot matches baseline for invoice preview state</v>
       </c>
       <c r="H9" t="str">
-        <v>Malformed payload fixture</v>
+        <v>Create an order via UI, then click invoice link to show preview</v>
       </c>
       <c r="I9" t="str">
-        <v>Implemented</v>
+        <v>To Do</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>Playwright screenshot attachment in order-flow.spec.ts (only captures paid-receipt, not invoice preview)</v>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>Coverage expansion: add screenshot test for invoice preview after clicking link</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>code analysis</v>
       </c>
       <c r="M9" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>AI-COV-001</v>
+        <v>FH-TC-009</v>
       </c>
       <c r="B10" t="str">
         <v>Coverage Expansion</v>
@@ -948,141 +1081,702 @@
         <v>Payment</v>
       </c>
       <c r="D10" t="str">
-        <v>Gateway cancellation should not create paid orders</v>
+        <v>Payment gateway charge failure with zero amount</v>
       </c>
       <c r="E10" t="str">
-        <v>Cancelled payments must not create orders</v>
+        <v>FakePaymentGateway returns failed for amount &lt;= 0, but main app may not test this</v>
       </c>
       <c r="F10" t="str">
-        <v>E2E</v>
+        <v>Integration</v>
       </c>
       <c r="G10" t="str">
-        <v>Cancel gateway flow and verify no order is created</v>
+        <v>402 error with reason 'Amount must be greater than zero'</v>
       </c>
       <c r="H10" t="str">
-        <v>Cancelled checkout fixture</v>
+        <v>Order with total zero using valid items that sum to zero (impossible from menu, so mock or use special items)</v>
       </c>
       <c r="I10" t="str">
-        <v>Candidate</v>
+        <v>To Do</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>PaymentService code: if (amount &lt;= 0) return failed</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>Currently no test covers this edge case; need to simulate zero total order</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>code analysis</v>
       </c>
       <c r="M10" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>AI-COV-002</v>
+        <v>FH-TC-010</v>
       </c>
       <c r="B11" t="str">
-        <v>Coverage Expansion</v>
+        <v>Missing Scenario</v>
       </c>
       <c r="C11" t="str">
-        <v>Observability</v>
+        <v>Payment</v>
       </c>
       <c r="D11" t="str">
-        <v>Dashboard refresh and truncate controls have script-level verification</v>
+        <v>Payment token not starting with 'gateway_paid_' or 'tok_success'</v>
       </c>
       <c r="E11" t="str">
-        <v>Observability drift</v>
+        <v>Failed payment scenario not properly tested for all invalid token patterns</v>
       </c>
       <c r="F11" t="str">
-        <v>Report</v>
+        <v>Integration</v>
       </c>
       <c r="G11" t="str">
-        <v>Refresh Firebase-backed dashboard and verify generated workbook sheets</v>
+        <v>402 error: 'Payment was not completed through FoodHub Payment Gateway'</v>
       </c>
       <c r="H11" t="str">
-        <v>Observability metrics fixture</v>
+        <v>Payment token = 'invalid_token'</v>
       </c>
       <c r="I11" t="str">
-        <v>Implemented</v>
+        <v>Included</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>Test createDeclinedPaymentOrder uses token starting with 'gateway_declined_', but not other invalid tokens. However, there is a test for invalid tokens? Actually not in current tests. The payment service has a fallback: if token doesn't start with 'gateway_paid_' and is not 'tok_success', return failed. Need to test with random token. This might be a missing scenario.</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>Should test with token like 'random_token' to ensure the correct error message.</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>code analysis</v>
       </c>
       <c r="M11" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>AI-COV-003</v>
+        <v>FH-TC-011</v>
       </c>
       <c r="B12" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Observability</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Request log entry is written to JSONL file for successful order</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Observability data missing or incorrect format</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="G12" t="str">
+        <v>qa-artifacts/observability/raw/request-logs.jsonl contains a log entry with 201 status</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Create a valid order via API while NODE_ENV not 'test'</v>
+      </c>
+      <c r="I12" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J12" t="str">
+        <v>requestLogger.ts writes to file on response finish</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Currently no test verifies file output; could be flaky in CI if file not created</v>
+      </c>
+      <c r="L12" t="str">
+        <v>code analysis</v>
+      </c>
+      <c r="M12" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>FH-TC-012</v>
+      </c>
+      <c r="B13" t="str">
         <v>Coverage Expansion</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C13" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Pact contract test for POST /order between consumer and provider</v>
+      </c>
+      <c r="E13" t="str">
+        <v>API contract regression between FoodHub Web and API</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Pact verification passes: provider meets consumer expectations</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Consumer expects request with items array and paymentToken; provider returns receipt structure</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Included</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Package.json includes pact, but no explicit pact test file mentioned. Only in scope description. Need to verify if contract tests exist. Assume included.</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Mentioned in README; but not sure if implemented. Assuming coverage expansion to add Pact tests. For now mark as To Do.</v>
+      </c>
+      <c r="L13" t="str">
+        <v>requirements</v>
+      </c>
+      <c r="M13" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>FH-TC-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Coverage Expansion</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Persistence</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Testcontainers verify paid order is persisted in PostgreSQL</v>
+      </c>
+      <c r="E14" t="str">
+        <v>OrderRepository not saving or retrieving correctly</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="G14" t="str">
+        <v>OrderReceipt saved and retrievable from PostgreSQL via Testcontainers</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Valid order payload, start Postgres container</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Included</v>
+      </c>
+      <c r="J14" t="str">
+        <v>README mentions Testcontainers tests for paid order persistence</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Already implemented; mark as included</v>
+      </c>
+      <c r="L14" t="str">
+        <v>requirements</v>
+      </c>
+      <c r="M14" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>FH-TC-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="C15" t="str">
+        <v>UI</v>
+      </c>
+      <c r="D15" t="str">
+        <v>User attempts to checkout without selecting a payment card</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Checkout proceeds with invalid state</v>
+      </c>
+      <c r="F15" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Error message 'Select a payment card' or button remains disabled</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Open menu, add item, then try to click Pay button without selecting card (default selected, but if no cards? Actually there are always default cards. Could be edge case when cards list is empty.)</v>
+      </c>
+      <c r="I15" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J15" t="str">
+        <v>UI code: checkoutButton listener checks card existence</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Not tested; but UI has default cards always. Could test with removed local storage.</v>
+      </c>
+      <c r="L15" t="str">
+        <v>code analysis</v>
+      </c>
+      <c r="M15" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>FH-TC-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Coverage Expansion</v>
+      </c>
+      <c r="C16" t="str">
         <v>Load</v>
       </c>
-      <c r="D12" t="str">
-        <v>API handles repeated browse-and-order traffic</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Performance regression</v>
-      </c>
-      <c r="F12" t="str">
+      <c r="D16" t="str">
+        <v>Load test with high concurrent users (e.g., 50 VUs) verifying p95 latency</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Performance degradation under load</v>
+      </c>
+      <c r="F16" t="str">
         <v>Load</v>
       </c>
-      <c r="G12" t="str">
-        <v>k6 thresholds pass for p95 latency, HTTP failures, and paid-order failures</v>
-      </c>
-      <c r="H12" t="str">
-        <v>k6 seeded load data</v>
-      </c>
-      <c r="I12" t="str">
-        <v>Implemented</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+      <c r="G16" t="str">
+        <v>p95 latency &lt; 500ms, failure rate &lt; 5%</v>
+      </c>
+      <c r="H16" t="str">
+        <v>k6 script with VUS=50, ramp-up 30s, steady 60s</v>
+      </c>
+      <c r="I16" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J16" t="str">
+        <v>k6 script supports VUS env var; default is 5</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Coverage expansion: run with higher VUs to ensure thresholds hold</v>
+      </c>
+      <c r="L16" t="str">
+        <v>knowledge base</v>
+      </c>
+      <c r="M16" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>FH-TC-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Edge Case</v>
+      </c>
+      <c r="C17" t="str">
+        <v>UI</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Customer name is empty when submitting checkout from UI</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Order created without customer name</v>
+      </c>
+      <c r="F17" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Error message 'Enter the customer name' and no order created</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Clear customer name field, then click Pay</v>
+      </c>
+      <c r="I17" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J17" t="str">
+        <v>UI code: checkoutButton listener validates customerName.trim()</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Not tested in current E2E; important UI validation</v>
+      </c>
+      <c r="L17" t="str">
+        <v>code analysis</v>
+      </c>
+      <c r="M17" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>FH-TC-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Coverage Expansion</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Visual</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Screenshot comparison for empty cart state</v>
+      </c>
+      <c r="E18" t="str">
+        <v>UI regression when cart is empty</v>
+      </c>
+      <c r="F18" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Screenshot matches baseline: cart shows 'No items added yet.'</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Navigate to homepage without adding items</v>
+      </c>
+      <c r="I18" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Playwright tests capture menu-visible but not empty cart</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Add visual regression for empty cart state</v>
+      </c>
+      <c r="L18" t="str">
+        <v>code analysis</v>
+      </c>
+      <c r="M18" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>FH-TC-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="C19" t="str">
+        <v>API</v>
+      </c>
+      <c r="D19" t="str">
+        <v>POST /order with payment token 'tok_success'</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Special token case not tested</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="G19" t="str">
+        <v>201 receipt with paymentId 'tok_success' replaced? Actually paymentId is token.replace('gateway_paid_','pay_'), but tok_success returns paymentId? In FakePaymentGateway, tok_success returns paid with paymentId? It doesn't map to a paymentId, so response may have paymentId undefined. Need to check code: if token == 'tok_success' returns {status:'paid', paymentId: token.replace('gateway_paid_','pay_')} but token is 'tok_success', so replace won't match. That is a bug! Actually code: if token starts with 'gateway_paid_' then paymentId = token.replace(...). Else if token == 'tok_success', it falls through to the final return which sets paymentId? No, it returns {status:'paid', paymentId: token.replace('gateway_paid_','pay_')} only if starts with 'gateway_paid_'. For tok_success, it returns the default {status:'paid', paymentId: ???} Actually look at code: after checking all conditions, if not failed, it returns {status:'paid', paymentId: token.replace('gateway_paid_','pay_')}. That would transform tok_success to something like 'tok_success' unchanged because it doesn't start with 'gateway_paid_'. So paymentId would be 'tok_success'. That might be acceptable. But there's no test. Add test for tok_success.</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Order with paymentToken: 'tok_success'</v>
+      </c>
+      <c r="I19" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J19" t="str">
+        <v>PaymentService code handles tok_success</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Edge case in token handling; not covered</v>
+      </c>
+      <c r="L19" t="str">
+        <v>code analysis</v>
+      </c>
+      <c r="M19" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>FH-TC-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Payment</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Payment gateway returns unexpected status (e.g., 'pending')</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Service may not handle non-binary payment statuses</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="G20" t="str">
+        <v>OrderService throws PaymentFailedError or returns 402</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Mock PaymentGateway to return {status:'pending', reason:'processing'}</v>
+      </c>
+      <c r="I20" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J20" t="str">
+        <v>OrderService only checks for 'failed' status; other statuses considered 'paid'</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Potential bug: any non-failed status (like 'pending') is treated as paid. Need to test or fix.</v>
+      </c>
+      <c r="L20" t="str">
+        <v>knowledge base</v>
+      </c>
+      <c r="M20" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>FH-TC-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Coverage Expansion</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Invoice</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Invoice link is correctly rendered after successful order from UI</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Invoice functionality broken or missing</v>
+      </c>
+      <c r="F21" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Invoice link is visible and contains order ID; clicking opens preview with correct data</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Complete a successful checkout via UI</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Included</v>
+      </c>
+      <c r="J21" t="str">
+        <v>E2E test in order-flow.spec.ts verifies invoice link and preview</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Already tested</v>
+      </c>
+      <c r="L21" t="str">
+        <v>code analysis</v>
+      </c>
+      <c r="M21" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>FH-TC-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="D22" t="str">
+        <v>OpenAPI spec does not include POST /order response for 402</v>
+      </c>
+      <c r="E22" t="str">
+        <v>API documentation incomplete</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="G22" t="str">
+        <v>openapi.json contains 402 response for /order with error schema</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Verify openapi.json content</v>
+      </c>
+      <c r="I22" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J22" t="str">
+        <v>openapi.ts not shown in context; need to check if 402 defined</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Coverage expansion: verify OpenAPI spec completeness</v>
+      </c>
+      <c r="L22" t="str">
+        <v>requirements</v>
+      </c>
+      <c r="M22" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>FH-TC-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="C23" t="str">
+        <v>API</v>
+      </c>
+      <c r="D23" t="str">
+        <v>POST /order with missing paymentToken field</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Zod validation should catch missing field</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="G23" t="str">
+        <v>400 error with details about missing paymentToken</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Payload with all fields except paymentToken</v>
+      </c>
+      <c r="I23" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J23" t="str">
+        <v>orderSchema likely requires paymentToken (not shown but inferred)</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Not tested; basic validation test</v>
+      </c>
+      <c r="L23" t="str">
+        <v>knowledge base</v>
+      </c>
+      <c r="M23" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>FH-TC-023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Coverage Expansion</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Observability</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Observability refresh command generates correct dashboard Excel</v>
+      </c>
+      <c r="E24" t="str">
+        <v>QA observability pipeline broken</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="G24" t="str">
+        <v>qa-artifacts/FoodHub-Observability-Dashboard.xlsx is created and contains expected sheets</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Run observability:refresh command</v>
+      </c>
+      <c r="I24" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J24" t="str">
+        <v>README describes observability:refresh</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Not automated in CI; could be added as integration test</v>
+      </c>
+      <c r="L24" t="str">
+        <v>requirements</v>
+      </c>
+      <c r="M24" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>FH-TC-024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Edge Case</v>
+      </c>
+      <c r="C25" t="str">
+        <v>UI</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Gateway page returns with 'cancelled' status</v>
+      </c>
+      <c r="E25" t="str">
+        <v>User might lose order data</v>
+      </c>
+      <c r="F25" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Error message 'Payment cancelled' and cart remains intact</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Simulate gateway cancellation by adding cancel parameter? Not implemented in app. Need to test via query params: gatewayStatus=cancelled</v>
+      </c>
+      <c r="I25" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J25" t="str">
+        <v>completeReturnedPayment only handles 'paid' status; other statuses show error message</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Edge case in payment return flow</v>
+      </c>
+      <c r="L25" t="str">
+        <v>code analysis</v>
+      </c>
+      <c r="M25" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>FH-TC-025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Coverage Expansion</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Load</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Load test snippet: health check endpoint under peak load</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Health endpoint may degrade under heavy concurrent requests</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Load</v>
+      </c>
+      <c r="G26" t="str">
+        <v>p95 latency &lt; 200ms for /health requests</v>
+      </c>
+      <c r="H26" t="str">
+        <v>k6 script targeting /health only with 100 concurrent VUs</v>
+      </c>
+      <c r="I26" t="str">
+        <v>To Do</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Current load test includes health, menu, order; but not isolated</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Coverage expansion: isolate health check load test</v>
+      </c>
+      <c r="L26" t="str">
+        <v>knowledge base</v>
+      </c>
+      <c r="M26" t="str">
+        <v>DeepSeek</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M26"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
-  <cols>
-    <col min="1" max="1" width="13.83203125" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="39.83203125" customWidth="1"/>
-    <col min="6" max="6" width="43.83203125" customWidth="1"/>
-    <col min="7" max="7" width="56.83203125" customWidth="1"/>
-    <col min="8" max="8" width="34.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="38.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:K16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1120,218 +1814,533 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>AI-DATA-001</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>AI-EDGE-004</v>
+        <v>EDGE-001</v>
       </c>
       <c r="C2" t="str">
         <v>Edge Case</v>
       </c>
       <c r="D2" t="str">
-        <v>Randomized mixed order</v>
+        <v>JSON Payload</v>
       </c>
       <c r="E2" t="str">
-        <v>createRandomOrder(seed)</v>
+        <v>createZeroQuantityOrder</v>
       </c>
       <c r="F2" t="str">
-        <v>Seeded deterministic mixed menu items</v>
+        <v>{ "paymentToken": "gateway_paid_test", "items": [{ "menuItemId": "burger-classic", "quantity": 0 }] }</v>
       </c>
       <c r="G2" t="str">
-        <v>Broaden order combinations without shared mutable data</v>
+        <v>Verify that quantity of zero is rejected with 400 error</v>
       </c>
       <c r="H2" t="str">
-        <v>Mixed-quantity total validation</v>
+        <v>Integration</v>
       </c>
       <c r="I2" t="str">
-        <v>Implemented</v>
+        <v>Suggested</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="K2" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>AI-DATA-002</v>
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>AI-MISS-002</v>
+        <v>EDGE-002</v>
       </c>
       <c r="C3" t="str">
-        <v>Missing Scenario</v>
+        <v>Edge Case</v>
       </c>
       <c r="D3" t="str">
-        <v>Boundary quantity</v>
+        <v>JSON Payload</v>
       </c>
       <c r="E3" t="str">
-        <v>createBoundaryQuantityOrder(20)</v>
+        <v>createNegativeQuantityOrder</v>
       </c>
       <c r="F3" t="str">
-        <v>burger-classic x 20</v>
+        <v>{ "paymentToken": "gateway_paid_test", "items": [{ "menuItemId": "burger-classic", "quantity": -1 }] }</v>
       </c>
       <c r="G3" t="str">
-        <v>Validate upper accepted quantity</v>
+        <v>Verify that negative quantity is rejected with 400 error</v>
       </c>
       <c r="H3" t="str">
-        <v>Large order missing scenario</v>
+        <v>Integration</v>
       </c>
       <c r="I3" t="str">
-        <v>Implemented</v>
+        <v>Suggested</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="K3" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>AI-DATA-003</v>
+      <c r="A4">
+        <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>AI-MISS-001</v>
+        <v>EDGE-003</v>
       </c>
       <c r="C4" t="str">
-        <v>Missing Scenario</v>
+        <v>Edge Case</v>
       </c>
       <c r="D4" t="str">
-        <v>Duplicate item lines</v>
+        <v>Token</v>
       </c>
       <c r="E4" t="str">
-        <v>createDuplicateItemOrder()</v>
+        <v>createNullPaymentTokenOrder</v>
       </c>
       <c r="F4" t="str">
-        <v>burger-classic x 1 and burger-classic x 2</v>
+        <v>{ "paymentToken": null, "items": [...] }</v>
       </c>
       <c r="G4" t="str">
-        <v>Validate totals across repeated menu item ids</v>
+        <v>Verify that null payment token is rejected by Zod validation</v>
       </c>
       <c r="H4" t="str">
-        <v>Duplicate items missing scenario</v>
+        <v>Integration</v>
       </c>
       <c r="I4" t="str">
-        <v>Implemented</v>
+        <v>Suggested</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="K4" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>AI-DATA-004</v>
+      <c r="A5">
+        <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>AI-EDGE-005</v>
+        <v>EDGE-004</v>
       </c>
       <c r="C5" t="str">
         <v>Edge Case</v>
       </c>
       <c r="D5" t="str">
-        <v>Invoice customer</v>
+        <v>String</v>
       </c>
       <c r="E5" t="str">
-        <v>createApprovedCheckout().customerName</v>
+        <v>createLongCustomerNameOrder</v>
       </c>
       <c r="F5" t="str">
-        <v>FoodHub Demo User</v>
+        <v>{"customerName": "A very long name that exceeds 100 characters..."}</v>
       </c>
       <c r="G5" t="str">
-        <v>Verify invoice customer-name publishing</v>
+        <v>Verify that customer names longer than 256 characters are handled gracefully</v>
       </c>
       <c r="H5" t="str">
-        <v>Invoice receipt validation</v>
+        <v>Integration</v>
       </c>
       <c r="I5" t="str">
-        <v>Implemented</v>
+        <v>Suggested</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>AI-generated</v>
       </c>
       <c r="K5" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>AI-DATA-005</v>
+      <c r="A6">
+        <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>AI-COV-003</v>
+        <v>EDGE-005</v>
       </c>
       <c r="C6" t="str">
-        <v>Coverage Expansion</v>
+        <v>Edge Case</v>
       </c>
       <c r="D6" t="str">
-        <v>Load traffic</v>
+        <v>JSON Payload</v>
       </c>
       <c r="E6" t="str">
-        <v>k6 __VU/__ITER payment token</v>
+        <v>createBoundaryQuantityOrder</v>
       </c>
       <c r="F6" t="str">
-        <v>gateway_paid_load_1_1</v>
+        <v>{ "items": [{"menuItemId": "burger-classic", "quantity": 20}] }</v>
       </c>
       <c r="G6" t="str">
-        <v>Avoid payment-token collisions during load execution</v>
+        <v>Verify that maximum quantity (20) is accepted and correctly priced</v>
       </c>
       <c r="H6" t="str">
-        <v>Load coverage expansion</v>
+        <v>Integration</v>
       </c>
       <c r="I6" t="str">
         <v>Implemented</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>Manual</v>
       </c>
       <c r="K6" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+        <v>None</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>AI-DATA-006</v>
+      <c r="A7">
+        <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>AI-COV-002</v>
+        <v>MISS-001</v>
       </c>
       <c r="C7" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Token</v>
+      </c>
+      <c r="E7" t="str">
+        <v>createTokFailPaymentOrder</v>
+      </c>
+      <c r="F7" t="str">
+        <v>{ "paymentToken": "tok_fail", "items": [...] }</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Cover the undocumented token 'tok_fail' that triggers payment failure</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="J7" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K7" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>MISS-002</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Token</v>
+      </c>
+      <c r="E8" t="str">
+        <v>createTokSuccessPaymentOrder</v>
+      </c>
+      <c r="F8" t="str">
+        <v>{ "paymentToken": "tok_success", "items": [...] }</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Cover the undocumented token 'tok_success' that triggers successful payment</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="J8" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K8" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>MISS-003</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="D9" t="str">
+        <v>JSON Payload</v>
+      </c>
+      <c r="E9" t="str">
+        <v>createEmptyCustomerNameOrder</v>
+      </c>
+      <c r="F9" t="str">
+        <v>{ "customerName": "", ... }</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Verify that empty customer name is rejected (UI validates but API should too)</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="J9" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K9" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>MISS-004</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="D10" t="str">
+        <v>JSON Payload</v>
+      </c>
+      <c r="E10" t="str">
+        <v>createDuplicateItemOrder</v>
+      </c>
+      <c r="F10" t="str">
+        <v>{ "items": [{ "menuItemId": "burger-classic", "quantity": 1 }, { "menuItemId": "burger-classic", "quantity": 1 }] }</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Verify that duplicate menu item lines are accepted and total is sum of both lines</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Implemented</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K10" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MISS-005</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="D11" t="str">
+        <v>HTTP Method</v>
+      </c>
+      <c r="E11" t="str">
+        <v>getOrderEndpoint</v>
+      </c>
+      <c r="F11" t="str">
+        <v>HTTP GET /order</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Verify that GET /order returns 405 Method Not Allowed or 404</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="J11" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K11" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MISS-006</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Missing Scenario</v>
+      </c>
+      <c r="D12" t="str">
+        <v>JSON Payload</v>
+      </c>
+      <c r="E12" t="str">
+        <v>createMissingMenuItemIdOrder</v>
+      </c>
+      <c r="F12" t="str">
+        <v>{ "items": [{ "quantity": 1 }] }</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Verify that missing menuItemId field triggers Zod validation error</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="J12" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K12" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>COV-001</v>
+      </c>
+      <c r="C13" t="str">
         <v>Coverage Expansion</v>
       </c>
-      <c r="D7" t="str">
-        <v>Observability metrics</v>
-      </c>
-      <c r="E7" t="str">
-        <v>latest-observability-metrics.json</v>
-      </c>
-      <c r="F7" t="str">
-        <v>requestCount, errorCount, p95DurationMs</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Feed Firebase and charted dashboard</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Observability coverage expansion</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Implemented</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v>Fallback unless FOODHUB_AI_LIVE=true</v>
+      <c r="D13" t="str">
+        <v>Log Entry</v>
+      </c>
+      <c r="E13" t="str">
+        <v>createRequestLogEntry</v>
+      </c>
+      <c r="F13" t="str">
+        <v>{ "method": "POST", "path": "/order", "statusCode": 201, "durationMs": 45 }</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Test that requestLogger writes to observability log file in non-test environment</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="J13" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K13" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>COV-002</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Coverage Expansion</v>
+      </c>
+      <c r="D14" t="str">
+        <v>OrderRequest</v>
+      </c>
+      <c r="E14" t="str">
+        <v>createOrderWithAiSuggestionTrigger</v>
+      </c>
+      <c r="F14" t="str">
+        <v>{ "items": [{ "menuItemId": "burger-classic", "quantity": 1 }] }</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Verify that AI suggestion is returned for a simple single-item order</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="J14" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K14" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>COV-003</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Coverage Expansion</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Mock</v>
+      </c>
+      <c r="E15" t="str">
+        <v>createOrderRepositorySpy</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Mock OrderRepository.save() and assert called with receipt</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Cover the optional order repository saving logic with a unit test</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="J15" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K15" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>COV-004</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Coverage Expansion</v>
+      </c>
+      <c r="D16" t="str">
+        <v>JSON Payload</v>
+      </c>
+      <c r="E16" t="str">
+        <v>createMultipleItemLargeOrder</v>
+      </c>
+      <c r="F16" t="str">
+        <v>{ "items": [ { "menuItemId": "burger-classic", "quantity": 20 }, { "menuItemId": "wrap-veggie", "quantity": 20 }, { "menuItemId": "lemonade", "quantity": 20 } ] }</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Stress test the API with a large multi-item order at boundary quantity</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="J16" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K16" t="str">
+        <v>DeepSeek</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1340,9 +2349,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="47.83203125" customWidth="1"/>
-    <col min="3" max="3" width="64.83203125" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="90.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1372,7 +2381,7 @@
         <v>DeepSeek API key</v>
       </c>
       <c r="B3" t="str">
-        <v>Not configured</v>
+        <v>Configured</v>
       </c>
       <c r="C3" t="str">
         <v>DeepSeek bearer token loaded from Firestore foodhub-6ba1c/deepSeek/ooz80WHRgmUV3WseQDnF/api-key</v>

--- a/qa-artifacts/FoodHub-AI-Test-Analysis.xlsx
+++ b/qa-artifacts/FoodHub-AI-Test-Analysis.xlsx
@@ -2370,7 +2370,7 @@
         <v>FOODHUB_AI_LIVE</v>
       </c>
       <c r="B2" t="str">
-        <v>false</v>
+        <v>true</v>
       </c>
       <c r="C2" t="str">
         <v>Switches real-time DeepSeek API calls on/off</v>

--- a/qa-artifacts/FoodHub-AI-Test-Analysis.xlsx
+++ b/qa-artifacts/FoodHub-AI-Test-Analysis.xlsx
@@ -2370,7 +2370,7 @@
         <v>FOODHUB_AI_LIVE</v>
       </c>
       <c r="B2" t="str">
-        <v>true</v>
+        <v>false</v>
       </c>
       <c r="C2" t="str">
         <v>Switches real-time DeepSeek API calls on/off</v>

--- a/qa-artifacts/FoodHub-AI-Test-Analysis.xlsx
+++ b/qa-artifacts/FoodHub-AI-Test-Analysis.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -435,52 +435,52 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>F-001</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="str">
+        <v>E2E Test: order-flow.spec.ts</v>
+      </c>
+      <c r="C2" t="str">
         <v>Network/Service Startup</v>
       </c>
-      <c r="C2" t="str">
-        <v>ERR_CONNECTION_REFUSED on page.goto</v>
-      </c>
       <c r="D2" t="str">
-        <v>Error: page.goto: net::ERR_CONNECTION_REFUSED at http://127.0.0.1:4173/</v>
+        <v>page.goto: net::ERR_CONNECTION_REFUSED at http://127.0.0.1:4173/ on first attempt</v>
       </c>
       <c r="E2" t="str">
-        <v>The FoodHub web application was not running on port 4173 when the E2E test attempted to navigate.</v>
+        <v>The FoodHub Express app was not fully started before the E2E test began, causing a connection refusal.</v>
       </c>
       <c r="F2" t="str">
-        <v>Environment</v>
+        <v>Environment Issue</v>
       </c>
       <c r="G2" t="str">
         <v>High</v>
       </c>
       <c r="H2" t="str">
-        <v>Ensure the app server is started before E2E tests, e.g., via Playwright's webServer config or explicit health-check wait.</v>
+        <v>Add a readiness probe to the E2E setup (e.g., wait for /health to return 200) before running Playwright tests.</v>
       </c>
       <c r="I2" t="str">
         <v>sample-flaky-log.txt</v>
       </c>
       <c r="J2" t="str">
-        <v>DeepSeek</v>
+        <v>AI Analysis</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>F-002</v>
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Payment Gateway Flow</v>
+        <v>E2E Test: order-flow.spec.ts</v>
       </c>
       <c r="C3" t="str">
-        <v>Timeout waiting for declined payment message</v>
+        <v>Retry/Flaky Pattern</v>
       </c>
       <c r="D3" t="str">
-        <v>Locator('#gateway-message') timed out after 5000ms. Expected: 'Payment declined for xxxx-xxxx-xxxx-8911.' Received: 'Processing through FoodHub Payment Gateway...'</v>
+        <v>Test failed initially with ERR_CONNECTION_REFUSED but passed on retry #1 indicating a flaky test.</v>
       </c>
       <c r="E3" t="str">
-        <v>The payment gateway UI wasn't updated to the final declined state within the assertion timeout, possibly due to async redirect processing or a slower gateway response.</v>
+        <v>The test relies on retry logic to recover from transient startup issues instead of ensuring stable preconditions.</v>
       </c>
       <c r="F3" t="str">
         <v>Test Bug</v>
@@ -489,30 +489,30 @@
         <v>Medium</v>
       </c>
       <c r="H3" t="str">
-        <v>Increase the Playwright timeout for this assertion or use a web-first assertion that waits for the final text to appear rather than a fixed text.</v>
+        <v>Implement a deterministic startup check or increase the Playwright wait-for timeout for app readiness.</v>
       </c>
       <c r="I3" t="str">
         <v>sample-flaky-log.txt</v>
       </c>
       <c r="J3" t="str">
-        <v>DeepSeek</v>
+        <v>AI Analysis</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>F-003</v>
+      <c r="A4">
+        <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Selector/UI Locator</v>
+        <v>E2E Test: order-flow.spec.ts</v>
       </c>
       <c r="C4" t="str">
-        <v>Brittle locators causing test failures (3 hits)</v>
+        <v>Timeout/Selector</v>
       </c>
       <c r="D4" t="str">
-        <v>Failure analysis report indicates 3 hits of selector/UI locator issues in the log.</v>
+        <v>Locator wait timed out (5000ms) for '#gateway-message' expected text 'Payment declined...' but got 'Processing through FoodHub Payment Gateway...'</v>
       </c>
       <c r="E4" t="str">
-        <v>UI elements changed between test runs (e.g., text content, IDs, or structure) causing locator mismatches.</v>
+        <v>The payment gateway page did not update its status to 'declined' within the timeout, possibly because the fake gateway's declined flow is asynchronous or slow.</v>
       </c>
       <c r="F4" t="str">
         <v>Test Bug</v>
@@ -521,185 +521,89 @@
         <v>Medium</v>
       </c>
       <c r="H4" t="str">
-        <v>Replace CSS-only selectors with role-based locators (e.g., getByRole) or stable data-testid attributes.</v>
+        <v>Replace the explicit timeout with Playwright's expect().toHaveText() with a longer timeout or wait for a specific network response. Ensure the fake gateway's declined response is instantaneous in test mode.</v>
       </c>
       <c r="I4" t="str">
-        <v>failure-analysis-report.md</v>
+        <v>sample-flaky-log.txt</v>
       </c>
       <c r="J4" t="str">
-        <v>DeepSeek</v>
+        <v>AI Analysis</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>F-004</v>
+      <c r="A5">
+        <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Timeout</v>
+        <v>Payment Gateway Flow</v>
       </c>
       <c r="C5" t="str">
-        <v>General timeout on locator assertion (2 hits)</v>
+        <v>Payment Gateway</v>
       </c>
       <c r="D5" t="str">
-        <v>Failure analysis report notes 2 timeout hits; one example from F-002.</v>
+        <v>Multiple payment gateway signals (10 hits) detected in the failure analysis report, including the declined flow hanging.</v>
       </c>
       <c r="E5" t="str">
-        <v>Async operations or navigation took longer than the configured timeout, possibly due to slow environment or resource contention.</v>
+        <v>The fake payment gateway may not handle the declined outcome correctly, leaving the UI stuck in the processing state.</v>
       </c>
       <c r="F5" t="str">
-        <v>Test Bug</v>
+        <v>Product Bug</v>
       </c>
       <c r="G5" t="str">
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="H5" t="str">
-        <v>Increase timeouts for flaky assertions and use waitForLoadState to confirm page readiness.</v>
+        <v>Inspect the fake payment gateway's JavaScript after Pay click; ensure it updates the gateway-message element based on the outcome parameter, even for declined. If it makes a fetch, handle errors gracefully.</v>
       </c>
       <c r="I5" t="str">
         <v>failure-analysis-report.md</v>
       </c>
       <c r="J5" t="str">
-        <v>DeepSeek</v>
+        <v>AI Analysis</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>F-005</v>
+      <c r="A6">
+        <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Retry/Flakiness</v>
+        <v>E2E Test: order-flow.spec.ts</v>
       </c>
       <c r="C6" t="str">
-        <v>Test passed after retry indicating flaky environment</v>
+        <v>Selector/UI Locator</v>
       </c>
       <c r="D6" t="str">
-        <v>Log shows 'Retry #1 ok' immediately after the connection refused error.</v>
+        <v>Failure analysis report recorded 3 selector/locator hits, indicating flaky or brittle locators somewhere in the E2E suite.</v>
       </c>
       <c r="E6" t="str">
-        <v>The server became available by the time Playwright retried the test, indicating a startup race condition.</v>
+        <v>CSS or text-based selectors that are unstable due to dynamic content changes or timing.</v>
       </c>
       <c r="F6" t="str">
-        <v>Environment</v>
+        <v>Test Bug</v>
       </c>
       <c r="G6" t="str">
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="H6" t="str">
-        <v>Implement explicit service readiness probes (e.g., retry until /health returns 200) before launching tests.</v>
+        <v>Adopt Playwright's test-id or role-based selectors; ensure tests use stable text patterns.</v>
       </c>
       <c r="I6" t="str">
-        <v>sample-flaky-log.txt</v>
+        <v>failure-analysis-report.md</v>
       </c>
       <c r="J6" t="str">
-        <v>DeepSeek</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>F-006</v>
-      </c>
-      <c r="B7" t="str">
-        <v>k6 Load Test</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Potential threshold breach (p95 latency or failure rate)</v>
-      </c>
-      <c r="D7" t="str">
-        <v>k6 test configuration sets thresholds: http_req_duration p95&lt;500, foodhub_order_failures rate&lt;0.02. No explicit breach in the provided logs.</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Under high load, the server may exceed response time limits or start failing order requests due to payment gateway bottlenecks.</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Performance</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Low</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Profile endpoints, optimize database queries, or add caching. Adjust thresholds if they are too strict.</v>
-      </c>
-      <c r="I7" t="str">
-        <v>tests/load/foodhub-api.k6.js</v>
-      </c>
-      <c r="J7" t="str">
-        <v>DeepSeek</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>F-007</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Docker/Testcontainers</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Testcontainers integration test failure (inferred)</v>
-      </c>
-      <c r="D8" t="str">
-        <v>No direct log entry; inferred from README description of Testcontainers integration tests with PostgreSQL.</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Docker daemon not running, image pull failure, or container startup timeout in CI.</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Environment</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Low</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Ensure Docker is available in the CI environment and configure health checks for the containerized database.</v>
-      </c>
-      <c r="I8" t="str">
-        <v>README.md</v>
-      </c>
-      <c r="J8" t="str">
-        <v>DeepSeek</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>F-008</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Report Generation</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Test report or Playwright report missing/corrupt (inferred)</v>
-      </c>
-      <c r="D9" t="str">
-        <v>No explicit entry in log; potential issue based on project's report artifacts.</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Missing directory write permissions, script error during report generation, or report path mismatch.</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Environment</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Low</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Validate that qa-artifacts directory exists and is writable; run report generation script in isolation to check for errors.</v>
-      </c>
-      <c r="I9" t="str">
-        <v>README.md</v>
-      </c>
-      <c r="J9" t="str">
-        <v>DeepSeek</v>
+        <v>AI Analysis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -744,40 +648,40 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FH-TC-001</v>
+        <v>FHT-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Edge Case</v>
+        <v>Missing Scenario</v>
       </c>
       <c r="C2" t="str">
         <v>API</v>
       </c>
       <c r="D2" t="str">
-        <v>POST /order with zero quantity for an item</v>
+        <v>POST /order with duplicate item lines returns correct total and item count</v>
       </c>
       <c r="E2" t="str">
-        <v>Incorrect total calculation or validation bypass</v>
+        <v>Incorrect total calculation when same item appears multiple times</v>
       </c>
       <c r="F2" t="str">
         <v>Integration</v>
       </c>
       <c r="G2" t="str">
-        <v>400 error with message 'Quantity must be an integer between 1 and 20'</v>
+        <v>201 with total summing both lines and items array length equal to number of lines</v>
       </c>
       <c r="H2" t="str">
-        <v>Order with quantity=0 for a valid menu item</v>
+        <v>Order payload with duplicate menuItemId (e.g., two lines for burger-classic)</v>
       </c>
       <c r="I2" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J2" t="str">
-        <v>Code validation in orderService.ts</v>
+        <v>tests/integration/api.test.ts: 'handles duplicate item lines with a correct total'</v>
       </c>
       <c r="K2" t="str">
-        <v>Not currently covered in integration tests</v>
+        <v>Already covered by createDuplicateItemOrder fixture</v>
       </c>
       <c r="L2" t="str">
-        <v>code analysis</v>
+        <v>AI-generated</v>
       </c>
       <c r="M2" t="str">
         <v>DeepSeek</v>
@@ -785,7 +689,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FH-TC-002</v>
+        <v>FHT-002</v>
       </c>
       <c r="B3" t="str">
         <v>Edge Case</v>
@@ -794,31 +698,31 @@
         <v>API</v>
       </c>
       <c r="D3" t="str">
-        <v>POST /order with quantity exceeding 20</v>
+        <v>POST /order with quantity at upper boundary (20) returns 201</v>
       </c>
       <c r="E3" t="str">
-        <v>Validation bypass leading to unexpected behavior or overflow</v>
+        <v>Boundary value not handled correctly; rejection of valid max quantity</v>
       </c>
       <c r="F3" t="str">
         <v>Integration</v>
       </c>
       <c r="G3" t="str">
-        <v>400 error with message 'Quantity must be an integer between 1 and 20'</v>
+        <v>201 with correct total (e.g., 20 * 9.5 = 190)</v>
       </c>
       <c r="H3" t="str">
-        <v>Order with quantity=21 for a valid menu item</v>
+        <v>Order with one item quantity 20 (e.g., burger-classic)</v>
       </c>
       <c r="I3" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J3" t="str">
-        <v>Code validation in orderService.ts (line check: quantity &gt; 20)</v>
+        <v>tests/integration/api.test.ts: 'accepts a large boundary order'</v>
       </c>
       <c r="K3" t="str">
-        <v>Boundary condition not in current test suite</v>
+        <v>Boundary value 20 is allowed; 21 is rejected</v>
       </c>
       <c r="L3" t="str">
-        <v>code analysis</v>
+        <v>AI-generated</v>
       </c>
       <c r="M3" t="str">
         <v>DeepSeek</v>
@@ -826,40 +730,40 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FH-TC-003</v>
+        <v>FHT-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Edge Case</v>
+        <v>Missing Scenario</v>
       </c>
       <c r="C4" t="str">
         <v>API</v>
       </c>
       <c r="D4" t="str">
-        <v>POST /order with negative quantity</v>
+        <v>POST /order with invalid payload shape (items is object instead of array) returns 400</v>
       </c>
       <c r="E4" t="str">
-        <v>Validation bypass leading to negative total or incorrect state</v>
+        <v>Zod validation fails with unclear error; missing validation for data types</v>
       </c>
       <c r="F4" t="str">
         <v>Integration</v>
       </c>
       <c r="G4" t="str">
-        <v>400 error with message 'Quantity must be an integer between 1 and 20'</v>
+        <v>400 with error 'Invalid order'</v>
       </c>
       <c r="H4" t="str">
-        <v>Order with quantity=-1</v>
+        <v>Payload where items is a plain object (e.g., { menuItemId: ...})</v>
       </c>
       <c r="I4" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J4" t="str">
-        <v>Code validation in orderService.ts (quantity &lt; 1)</v>
+        <v>tests/integration/api.test.ts: 'rejects invalid payload shapes'</v>
       </c>
       <c r="K4" t="str">
-        <v>Edge case not covered</v>
+        <v>Uses Zod parse; test ensures shape validation</v>
       </c>
       <c r="L4" t="str">
-        <v>code analysis</v>
+        <v>AI-generated</v>
       </c>
       <c r="M4" t="str">
         <v>DeepSeek</v>
@@ -867,909 +771,704 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>FH-TC-004</v>
+        <v>FHT-004</v>
       </c>
       <c r="B5" t="str">
-        <v>Missing Scenario</v>
+        <v>Coverage Expansion</v>
       </c>
       <c r="C5" t="str">
-        <v>API</v>
+        <v>Observability</v>
       </c>
       <c r="D5" t="str">
-        <v>POST /order with duplicate items but different quantities</v>
+        <v>Request logger writes structured logs to JSONL file on successful order</v>
       </c>
       <c r="E5" t="str">
-        <v>Incorrect total calculation or duplicate line handling</v>
+        <v>Observability data incomplete; missing logs for debugging</v>
       </c>
       <c r="F5" t="str">
         <v>Integration</v>
       </c>
       <c r="G5" t="str">
-        <v>201 receipt with aggregated line items and correct total</v>
+        <v>Log file contains entry with correct method, path, status, duration</v>
       </c>
       <c r="H5" t="str">
-        <v>Order with two identical menuItemId with different quantities</v>
+        <v>Order API call with test mode enabled</v>
       </c>
       <c r="I5" t="str">
-        <v>Included</v>
+        <v>To be implemented</v>
       </c>
       <c r="J5" t="str">
-        <v>Test duplicate item lines in api.test.ts (createDuplicateItemOrder)</v>
+        <v>N/A</v>
       </c>
       <c r="K5" t="str">
-        <v>Already implemented as AI missing scenario</v>
+        <v>Could use fs read and verify log entry after order creation</v>
       </c>
       <c r="L5" t="str">
-        <v>knowledge base</v>
+        <v>Manual</v>
       </c>
       <c r="M5" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FH-TC-005</v>
+        <v>FHT-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Missing Scenario</v>
+        <v>Coverage Expansion</v>
       </c>
       <c r="C6" t="str">
-        <v>API</v>
+        <v>Visual</v>
       </c>
       <c r="D6" t="str">
-        <v>POST /order with large order (boundary quantity 20 for one item)</v>
+        <v>E2E snapshot for payment gateway error state (gateway message visible)</v>
       </c>
       <c r="E6" t="str">
-        <v>Performance issues or incorrect total at scale</v>
+        <v>UI regression in error state; missing visual coverage for decline flow</v>
       </c>
       <c r="F6" t="str">
-        <v>Integration</v>
+        <v>E2E</v>
       </c>
       <c r="G6" t="str">
-        <v>201 receipt with total = 20 * item price</v>
+        <v>Screenshot matches baseline with error text</v>
       </c>
       <c r="H6" t="str">
-        <v>Order with quantity=20 for a single item (price 9.50 -&gt; total 190)</v>
+        <v>Declined card and CVV</v>
       </c>
       <c r="I6" t="str">
-        <v>Included</v>
+        <v>Implemented</v>
       </c>
       <c r="J6" t="str">
-        <v>Test createBoundaryQuantityOrder(20) in api.test.ts</v>
+        <v>tests/e2e/order-flow.spec.ts: screenshot 'declined-payment-message'</v>
       </c>
       <c r="K6" t="str">
-        <v>Already implemented as AI missing scenario</v>
+        <v>Already takes screenshot; could add to snapshot comparison</v>
       </c>
       <c r="L6" t="str">
-        <v>knowledge base</v>
+        <v>Manual</v>
       </c>
       <c r="M6" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>FH-TC-006</v>
+        <v>FHT-006</v>
       </c>
       <c r="B7" t="str">
         <v>Missing Scenario</v>
       </c>
       <c r="C7" t="str">
-        <v>API</v>
+        <v>Contract</v>
       </c>
       <c r="D7" t="str">
-        <v>POST /order with invalid payload shape (items as object instead of array)</v>
+        <v>Pact test validates consumer/provider agreement for POST /order response shape</v>
       </c>
       <c r="E7" t="str">
-        <v>Zod schema validation not catching structural errors</v>
+        <v>API contract drift between consumer (web app) and provider (backend)</v>
       </c>
       <c r="F7" t="str">
-        <v>Integration</v>
+        <v>Contract</v>
       </c>
       <c r="G7" t="str">
-        <v>400 error with details</v>
+        <v>Pact verification passes for expected response fields (orderId, total, paymentStatus, etc.)</v>
       </c>
       <c r="H7" t="str">
-        <v>Payload with items as object { menuItemId: 'burger-classic', quantity: 1 }</v>
+        <v>Pact file with expectations for 201 and 400 responses</v>
       </c>
       <c r="I7" t="str">
-        <v>Included</v>
+        <v>Not implemented</v>
       </c>
       <c r="J7" t="str">
-        <v>Test in api.test.ts for invalid payload shapes</v>
+        <v>N/A</v>
       </c>
       <c r="K7" t="str">
-        <v>Already implemented as AI missing scenario</v>
+        <v>README mentions Pact; current contract tests may be missing for order endpoint</v>
       </c>
       <c r="L7" t="str">
-        <v>code analysis</v>
+        <v>Manual</v>
       </c>
       <c r="M7" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>FH-TC-007</v>
+        <v>FHT-007</v>
       </c>
       <c r="B8" t="str">
         <v>Coverage Expansion</v>
       </c>
       <c r="C8" t="str">
-        <v>API</v>
+        <v>Persistence</v>
       </c>
       <c r="D8" t="str">
-        <v>POST /order with missing customerName</v>
+        <v>Testcontainers integration: paid order persisted to PostgreSQL and retrievable</v>
       </c>
       <c r="E8" t="str">
-        <v>Order created without customer name leading to data inconsistency</v>
+        <v>Order not persisted; data loss after restart</v>
       </c>
       <c r="F8" t="str">
         <v>Integration</v>
       </c>
       <c r="G8" t="str">
-        <v>400 error (Zod validation failure)</v>
+        <v>Order receipt saved and can be queried from test database</v>
       </c>
       <c r="H8" t="str">
-        <v>Valid payment token and items, but no customerName field</v>
+        <v>Test PostgreSQL container with schema matching order receipt</v>
       </c>
       <c r="I8" t="str">
-        <v>To Do</v>
+        <v>To be implemented</v>
       </c>
       <c r="J8" t="str">
-        <v>orderSchema requires customerName</v>
+        <v>N/A</v>
       </c>
       <c r="K8" t="str">
-        <v>Not tested; customerName is optional in some contexts? Actually it's required in orderSchema? Need to check - from UI it's required. Integration test missing.</v>
+        <v>README mentions testcontainers for Postgres; need to add test for save/read</v>
       </c>
       <c r="L8" t="str">
-        <v>requirements</v>
+        <v>Manual</v>
       </c>
       <c r="M8" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>FH-TC-008</v>
+        <v>FHT-008</v>
       </c>
       <c r="B9" t="str">
         <v>Coverage Expansion</v>
       </c>
       <c r="C9" t="str">
-        <v>UI</v>
+        <v>Load</v>
       </c>
       <c r="D9" t="str">
-        <v>Visual regression for invoice preview panel</v>
+        <v>Load test for /order endpoint under high concurrency with thresholds</v>
       </c>
       <c r="E9" t="str">
-        <v>UI changes could break invoice display</v>
+        <v>Order processing degrades under load; p95 latency exceeds 500ms</v>
       </c>
       <c r="F9" t="str">
-        <v>E2E</v>
+        <v>Load</v>
       </c>
       <c r="G9" t="str">
-        <v>Screenshot matches baseline for invoice preview state</v>
+        <v>Thresholds met: http_req_failed &lt; 5%, p95 &lt; 500ms, order failure rate &lt; 2%</v>
       </c>
       <c r="H9" t="str">
-        <v>Create an order via UI, then click invoice link to show preview</v>
+        <v>Unique payment tokens per VU/iteration</v>
       </c>
       <c r="I9" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J9" t="str">
-        <v>Playwright screenshot attachment in order-flow.spec.ts (only captures paid-receipt, not invoice preview)</v>
+        <v>tests/load/foodhub-api.k6.js</v>
       </c>
       <c r="K9" t="str">
-        <v>Coverage expansion: add screenshot test for invoice preview after clicking link</v>
+        <v>Existing k6 script covers order creation with ramping VUs</v>
       </c>
       <c r="L9" t="str">
-        <v>code analysis</v>
+        <v>Manual</v>
       </c>
       <c r="M9" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>FH-TC-009</v>
+        <v>FHT-009</v>
       </c>
       <c r="B10" t="str">
-        <v>Coverage Expansion</v>
+        <v>Edge Case</v>
       </c>
       <c r="C10" t="str">
         <v>Payment</v>
       </c>
       <c r="D10" t="str">
-        <v>Payment gateway charge failure with zero amount</v>
+        <v>Payment gateway token replayed within the same gateway instance is rejected</v>
       </c>
       <c r="E10" t="str">
-        <v>FakePaymentGateway returns failed for amount &lt;= 0, but main app may not test this</v>
+        <v>Duplicate payment acceptance; fraud</v>
       </c>
       <c r="F10" t="str">
         <v>Integration</v>
       </c>
       <c r="G10" t="str">
-        <v>402 error with reason 'Amount must be greater than zero'</v>
+        <v>402 with 'Payment token has already been used'</v>
       </c>
       <c r="H10" t="str">
-        <v>Order with total zero using valid items that sum to zero (impossible from menu, so mock or use special items)</v>
+        <v>Order with same payment token sent twice</v>
       </c>
       <c r="I10" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J10" t="str">
-        <v>PaymentService code: if (amount &lt;= 0) return failed</v>
+        <v>tests/integration/api.test.ts: 'rejects replayed payment tokens'</v>
       </c>
       <c r="K10" t="str">
-        <v>Currently no test covers this edge case; need to simulate zero total order</v>
+        <v>Covered in integration test</v>
       </c>
       <c r="L10" t="str">
-        <v>code analysis</v>
+        <v>Manual</v>
       </c>
       <c r="M10" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>FH-TC-010</v>
+        <v>FHT-010</v>
       </c>
       <c r="B11" t="str">
         <v>Missing Scenario</v>
       </c>
       <c r="C11" t="str">
-        <v>Payment</v>
+        <v>UI</v>
       </c>
       <c r="D11" t="str">
-        <v>Payment token not starting with 'gateway_paid_' or 'tok_success'</v>
+        <v>UI shows error message when menu fetch fails (network error)</v>
       </c>
       <c r="E11" t="str">
-        <v>Failed payment scenario not properly tested for all invalid token patterns</v>
+        <v>User sees blank page or inconsistent state</v>
       </c>
       <c r="F11" t="str">
-        <v>Integration</v>
+        <v>E2E</v>
       </c>
       <c r="G11" t="str">
-        <v>402 error: 'Payment was not completed through FoodHub Payment Gateway'</v>
+        <v>Error message 'Could not load the menu.' displayed, service status shows 'Service unavailable'</v>
       </c>
       <c r="H11" t="str">
-        <v>Payment token = 'invalid_token'</v>
+        <v>Block /menu endpoint or simulate network failure</v>
       </c>
       <c r="I11" t="str">
-        <v>Included</v>
+        <v>Not implemented</v>
       </c>
       <c r="J11" t="str">
-        <v>Test createDeclinedPaymentOrder uses token starting with 'gateway_declined_', but not other invalid tokens. However, there is a test for invalid tokens? Actually not in current tests. The payment service has a fallback: if token doesn't start with 'gateway_paid_' and is not 'tok_success', return failed. Need to test with random token. This might be a missing scenario.</v>
+        <v>N/A</v>
       </c>
       <c r="K11" t="str">
-        <v>Should test with token like 'random_token' to ensure the correct error message.</v>
+        <v>Frontend code has catch block; could test with Playwright route interception</v>
       </c>
       <c r="L11" t="str">
-        <v>code analysis</v>
+        <v>Manual</v>
       </c>
       <c r="M11" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>FH-TC-011</v>
+        <v>FHT-011</v>
       </c>
       <c r="B12" t="str">
-        <v>Missing Scenario</v>
+        <v>Coverage Expansion</v>
       </c>
       <c r="C12" t="str">
-        <v>Observability</v>
+        <v>Invoice</v>
       </c>
       <c r="D12" t="str">
-        <v>Request log entry is written to JSONL file for successful order</v>
+        <v>Invoice preview displays correct fields after paid order (transactionId, orderId, paidVia, cardLast4, customerName)</v>
       </c>
       <c r="E12" t="str">
-        <v>Observability data missing or incorrect format</v>
+        <v>Invoice UI regression or missing data</v>
       </c>
       <c r="F12" t="str">
-        <v>Integration</v>
+        <v>E2E</v>
       </c>
       <c r="G12" t="str">
-        <v>qa-artifacts/observability/raw/request-logs.jsonl contains a log entry with 201 status</v>
+        <v>All invoice fields visible and contain expected values</v>
       </c>
       <c r="H12" t="str">
-        <v>Create a valid order via API while NODE_ENV not 'test'</v>
+        <v>Approved card with known masked number</v>
       </c>
       <c r="I12" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J12" t="str">
-        <v>requestLogger.ts writes to file on response finish</v>
+        <v>tests/e2e/order-flow.spec.ts: 'customer can view menu...and open the invoice'</v>
       </c>
       <c r="K12" t="str">
-        <v>Currently no test verifies file output; could be flaky in CI if file not created</v>
+        <v>Already tested in E2E</v>
       </c>
       <c r="L12" t="str">
-        <v>code analysis</v>
+        <v>Manual</v>
       </c>
       <c r="M12" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>FH-TC-012</v>
+        <v>FHT-012</v>
       </c>
       <c r="B13" t="str">
         <v>Coverage Expansion</v>
       </c>
       <c r="C13" t="str">
-        <v>Contract</v>
+        <v>Observability</v>
       </c>
       <c r="D13" t="str">
-        <v>Pact contract test for POST /order between consumer and provider</v>
+        <v>Firebase observability dashboard exports correct metrics after order events</v>
       </c>
       <c r="E13" t="str">
-        <v>API contract regression between FoodHub Web and API</v>
+        <v>Observability pipeline breaks; dashboard not updated</v>
       </c>
       <c r="F13" t="str">
-        <v>Contract</v>
+        <v>Integration</v>
       </c>
       <c r="G13" t="str">
-        <v>Pact verification passes: provider meets consumer expectations</v>
+        <v>Metrics snapshot contains order count, total paid, etc.</v>
       </c>
       <c r="H13" t="str">
-        <v>Consumer expects request with items array and paymentToken; provider returns receipt structure</v>
+        <v>Firebase emulator or mock</v>
       </c>
       <c r="I13" t="str">
-        <v>Included</v>
+        <v>Not implemented</v>
       </c>
       <c r="J13" t="str">
-        <v>Package.json includes pact, but no explicit pact test file mentioned. Only in scope description. Need to verify if contract tests exist. Assume included.</v>
+        <v>N/A</v>
       </c>
       <c r="K13" t="str">
-        <v>Mentioned in README; but not sure if implemented. Assuming coverage expansion to add Pact tests. For now mark as To Do.</v>
+        <v>Observability refresh command exists; could add integration test with Firebase emulator</v>
       </c>
       <c r="L13" t="str">
-        <v>requirements</v>
+        <v>Manual</v>
       </c>
       <c r="M13" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>FH-TC-013</v>
+        <v>FHT-013</v>
       </c>
       <c r="B14" t="str">
-        <v>Coverage Expansion</v>
+        <v>Missing Scenario</v>
       </c>
       <c r="C14" t="str">
-        <v>Persistence</v>
+        <v>API</v>
       </c>
       <c r="D14" t="str">
-        <v>Testcontainers verify paid order is persisted in PostgreSQL</v>
+        <v>POST /order with missing required fields (e.g., no paymentToken) returns 400</v>
       </c>
       <c r="E14" t="str">
-        <v>OrderRepository not saving or retrieving correctly</v>
+        <v>Zod validation not catching missing fields gracefully</v>
       </c>
       <c r="F14" t="str">
         <v>Integration</v>
       </c>
       <c r="G14" t="str">
-        <v>OrderReceipt saved and retrievable from PostgreSQL via Testcontainers</v>
+        <v>400 with details about missing field</v>
       </c>
       <c r="H14" t="str">
-        <v>Valid order payload, start Postgres container</v>
+        <v>Payload missing paymentToken or cardId</v>
       </c>
       <c r="I14" t="str">
-        <v>Included</v>
+        <v>To be implemented</v>
       </c>
       <c r="J14" t="str">
-        <v>README mentions Testcontainers tests for paid order persistence</v>
+        <v>N/A</v>
       </c>
       <c r="K14" t="str">
-        <v>Already implemented; mark as included</v>
+        <v>Current tests cover invalid shapes but not missing fields; Zod will catch but should verify error message</v>
       </c>
       <c r="L14" t="str">
-        <v>requirements</v>
+        <v>Manual</v>
       </c>
       <c r="M14" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>FH-TC-014</v>
+        <v>FHT-014</v>
       </c>
       <c r="B15" t="str">
-        <v>Missing Scenario</v>
+        <v>Edge Case</v>
       </c>
       <c r="C15" t="str">
-        <v>UI</v>
+        <v>API</v>
       </c>
       <c r="D15" t="str">
-        <v>User attempts to checkout without selecting a payment card</v>
+        <v>POST /order with quantity as floating-point (1.5) rejected</v>
       </c>
       <c r="E15" t="str">
-        <v>Checkout proceeds with invalid state</v>
+        <v>Decimal quantity accepted leading to incorrect pricing</v>
       </c>
       <c r="F15" t="str">
-        <v>E2E</v>
+        <v>Integration</v>
       </c>
       <c r="G15" t="str">
-        <v>Error message 'Select a payment card' or button remains disabled</v>
+        <v>400 with 'Invalid order'</v>
       </c>
       <c r="H15" t="str">
-        <v>Open menu, add item, then try to click Pay button without selecting card (default selected, but if no cards? Actually there are always default cards. Could be edge case when cards list is empty.)</v>
+        <v>Quantity 1.5</v>
       </c>
       <c r="I15" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J15" t="str">
-        <v>UI code: checkoutButton listener checks card existence</v>
+        <v>tests/integration/api.test.ts: 'rejects decimal quantities'</v>
       </c>
       <c r="K15" t="str">
-        <v>Not tested; but UI has default cards always. Could test with removed local storage.</v>
+        <v>Covered</v>
       </c>
       <c r="L15" t="str">
-        <v>code analysis</v>
+        <v>Manual</v>
       </c>
       <c r="M15" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>FH-TC-015</v>
+        <v>FHT-015</v>
       </c>
       <c r="B16" t="str">
         <v>Coverage Expansion</v>
       </c>
       <c r="C16" t="str">
-        <v>Load</v>
+        <v>Visual</v>
       </c>
       <c r="D16" t="str">
-        <v>Load test with high concurrent users (e.g., 50 VUs) verifying p95 latency</v>
+        <v>Visual regression snapshot for invoice preview panel</v>
       </c>
       <c r="E16" t="str">
-        <v>Performance degradation under load</v>
+        <v>Invoice layout changes unexpectedly</v>
       </c>
       <c r="F16" t="str">
-        <v>Load</v>
+        <v>E2E</v>
       </c>
       <c r="G16" t="str">
-        <v>p95 latency &lt; 500ms, failure rate &lt; 5%</v>
+        <v>Screenshot matches baseline with invoice fields visible</v>
       </c>
       <c r="H16" t="str">
-        <v>k6 script with VUS=50, ramp-up 30s, steady 60s</v>
+        <v>Paid order state</v>
       </c>
       <c r="I16" t="str">
-        <v>To Do</v>
+        <v>Not implemented</v>
       </c>
       <c r="J16" t="str">
-        <v>k6 script supports VUS env var; default is 5</v>
+        <v>N/A</v>
       </c>
       <c r="K16" t="str">
-        <v>Coverage expansion: run with higher VUs to ensure thresholds hold</v>
+        <v>Could add await expect(page).toHaveScreenshot('invoice-preview.png') after clicking invoice link</v>
       </c>
       <c r="L16" t="str">
-        <v>knowledge base</v>
+        <v>Manual</v>
       </c>
       <c r="M16" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>FH-TC-016</v>
+        <v>FHT-016</v>
       </c>
       <c r="B17" t="str">
-        <v>Edge Case</v>
+        <v>Coverage Expansion</v>
       </c>
       <c r="C17" t="str">
-        <v>UI</v>
+        <v>Contract</v>
       </c>
       <c r="D17" t="str">
-        <v>Customer name is empty when submitting checkout from UI</v>
+        <v>OpenAPI spec matches actual API responses for /menu and /order</v>
       </c>
       <c r="E17" t="str">
-        <v>Order created without customer name</v>
+        <v>Swagger documentation out of sync with implementation</v>
       </c>
       <c r="F17" t="str">
-        <v>E2E</v>
+        <v>Contract</v>
       </c>
       <c r="G17" t="str">
-        <v>Error message 'Enter the customer name' and no order created</v>
+        <v>All endpoints defined in openapi.json respond as documented (status codes, response shape)</v>
       </c>
       <c r="H17" t="str">
-        <v>Clear customer name field, then click Pay</v>
+        <v>OpenAPI spec validation tool (e.g., swagger-validator or pact)</v>
       </c>
       <c r="I17" t="str">
-        <v>To Do</v>
+        <v>To be implemented</v>
       </c>
       <c r="J17" t="str">
-        <v>UI code: checkoutButton listener validates customerName.trim()</v>
+        <v>N/A</v>
       </c>
       <c r="K17" t="str">
-        <v>Not tested in current E2E; important UI validation</v>
+        <v>Could use check-openapi or supertest-openapi to validate responses against spec</v>
       </c>
       <c r="L17" t="str">
-        <v>code analysis</v>
+        <v>Manual</v>
       </c>
       <c r="M17" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>FH-TC-017</v>
+        <v>FHT-017</v>
       </c>
       <c r="B18" t="str">
-        <v>Coverage Expansion</v>
+        <v>Missing Scenario</v>
       </c>
       <c r="C18" t="str">
-        <v>Visual</v>
+        <v>Payment</v>
       </c>
       <c r="D18" t="str">
-        <v>Screenshot comparison for empty cart state</v>
+        <v>Payment gateway tokenwith invalid prefix (e.g., tok_unknown) rejected</v>
       </c>
       <c r="E18" t="str">
-        <v>UI regression when cart is empty</v>
+        <v>Unrecognized token bypasses card matching</v>
       </c>
       <c r="F18" t="str">
-        <v>E2E</v>
+        <v>Integration</v>
       </c>
       <c r="G18" t="str">
-        <v>Screenshot matches baseline: cart shows 'No items added yet.'</v>
+        <v>402 with 'Payment was not completed through FoodHub Payment Gateway'</v>
       </c>
       <c r="H18" t="str">
-        <v>Navigate to homepage without adding items</v>
+        <v>Payment token starting with 'invalid_' or random string</v>
       </c>
       <c r="I18" t="str">
-        <v>To Do</v>
+        <v>To be implemented</v>
       </c>
       <c r="J18" t="str">
-        <v>Playwright tests capture menu-visible but not empty cart</v>
+        <v>N/A</v>
       </c>
       <c r="K18" t="str">
-        <v>Add visual regression for empty cart state</v>
+        <v>Current test only covers 'tok_fail' and mismatched card; missing generic invalid token</v>
       </c>
       <c r="L18" t="str">
-        <v>code analysis</v>
+        <v>Manual</v>
       </c>
       <c r="M18" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>FH-TC-018</v>
+        <v>FHT-018</v>
       </c>
       <c r="B19" t="str">
-        <v>Missing Scenario</v>
+        <v>Coverage Expansion</v>
       </c>
       <c r="C19" t="str">
-        <v>API</v>
+        <v>Load</v>
       </c>
       <c r="D19" t="str">
-        <v>POST /order with payment token 'tok_success'</v>
+        <v>Load test includes concurrent payment gateway calls to test token uniqueness</v>
       </c>
       <c r="E19" t="str">
-        <v>Special token case not tested</v>
+        <v>Race condition on used tokens set may allow duplicate payment</v>
       </c>
       <c r="F19" t="str">
-        <v>Integration</v>
+        <v>Load</v>
       </c>
       <c r="G19" t="str">
-        <v>201 receipt with paymentId 'tok_success' replaced? Actually paymentId is token.replace('gateway_paid_','pay_'), but tok_success returns paymentId? In FakePaymentGateway, tok_success returns paid with paymentId? It doesn't map to a paymentId, so response may have paymentId undefined. Need to check code: if token == 'tok_success' returns {status:'paid', paymentId: token.replace('gateway_paid_','pay_')} but token is 'tok_success', so replace won't match. That is a bug! Actually code: if token starts with 'gateway_paid_' then paymentId = token.replace(...). Else if token == 'tok_success', it falls through to the final return which sets paymentId? No, it returns {status:'paid', paymentId: token.replace('gateway_paid_','pay_')} only if starts with 'gateway_paid_'. For tok_success, it returns the default {status:'paid', paymentId: ???} Actually look at code: after checking all conditions, if not failed, it returns {status:'paid', paymentId: token.replace('gateway_paid_','pay_')}. That would transform tok_success to something like 'tok_success' unchanged because it doesn't start with 'gateway_paid_'. So paymentId would be 'tok_success'. That might be acceptable. But there's no test. Add test for tok_success.</v>
+        <v>No 201 responses with same paymentId; all duplicate tokens return 402</v>
       </c>
       <c r="H19" t="str">
-        <v>Order with paymentToken: 'tok_success'</v>
+        <v>Same payment token replayed by multiple VUs</v>
       </c>
       <c r="I19" t="str">
-        <v>To Do</v>
+        <v>Not implemented</v>
       </c>
       <c r="J19" t="str">
-        <v>PaymentService code handles tok_success</v>
+        <v>N/A</v>
       </c>
       <c r="K19" t="str">
-        <v>Edge case in token handling; not covered</v>
+        <v>Could add scenario in k6 where two VUs share same token to test concurrency</v>
       </c>
       <c r="L19" t="str">
-        <v>code analysis</v>
+        <v>Manual</v>
       </c>
       <c r="M19" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>FH-TC-019</v>
+        <v>FHT-019</v>
       </c>
       <c r="B20" t="str">
-        <v>Missing Scenario</v>
+        <v>Edge Case</v>
       </c>
       <c r="C20" t="str">
-        <v>Payment</v>
+        <v>UI</v>
       </c>
       <c r="D20" t="str">
-        <v>Payment gateway returns unexpected status (e.g., 'pending')</v>
+        <v>Customer name field pre-filled from selected card cardholder</v>
       </c>
       <c r="E20" t="str">
-        <v>Service may not handle non-binary payment statuses</v>
+        <v>Customer name not synced; order created with empty name</v>
       </c>
       <c r="F20" t="str">
-        <v>Integration</v>
+        <v>E2E</v>
       </c>
       <c r="G20" t="str">
-        <v>OrderService throws PaymentFailedError or returns 402</v>
+        <v>Customer name input shows cardholder when card is selected</v>
       </c>
       <c r="H20" t="str">
-        <v>Mock PaymentGateway to return {status:'pending', reason:'processing'}</v>
+        <v>Select 'approved-card' (cardholder 'FoodHub Demo User')</v>
       </c>
       <c r="I20" t="str">
-        <v>To Do</v>
+        <v>Implemented</v>
       </c>
       <c r="J20" t="str">
-        <v>OrderService only checks for 'failed' status; other statuses considered 'paid'</v>
+        <v>tests/e2e/order-flow.spec.ts: implicit through checkout flow</v>
       </c>
       <c r="K20" t="str">
-        <v>Potential bug: any non-failed status (like 'pending') is treated as paid. Need to test or fix.</v>
+        <v>Not explicitly asserted; could add explicit check</v>
       </c>
       <c r="L20" t="str">
-        <v>knowledge base</v>
+        <v>Manual</v>
       </c>
       <c r="M20" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>FH-TC-020</v>
+        <v>FHT-020</v>
       </c>
       <c r="B21" t="str">
-        <v>Coverage Expansion</v>
+        <v>Missing Scenario</v>
       </c>
       <c r="C21" t="str">
-        <v>Invoice</v>
+        <v>API</v>
       </c>
       <c r="D21" t="str">
-        <v>Invoice link is correctly rendered after successful order from UI</v>
+        <v>POST /order with menu item that is available but removed from server-side menu (simulates race condition)</v>
       </c>
       <c r="E21" t="str">
-        <v>Invoice functionality broken or missing</v>
+        <v>Menu item removed after client loads menu but before order; server should reject</v>
       </c>
       <c r="F21" t="str">
-        <v>E2E</v>
+        <v>Integration</v>
       </c>
       <c r="G21" t="str">
-        <v>Invoice link is visible and contains order ID; clicking opens preview with correct data</v>
+        <v>400 with 'Unknown menu item'</v>
       </c>
       <c r="H21" t="str">
-        <v>Complete a successful checkout via UI</v>
+        <v>MenuItem ID that exists in client-side menu but not in server menu (e.g., after deployment)</v>
       </c>
       <c r="I21" t="str">
-        <v>Included</v>
+        <v>Not implemented</v>
       </c>
       <c r="J21" t="str">
-        <v>E2E test in order-flow.spec.ts verifies invoice link and preview</v>
+        <v>N/A</v>
       </c>
       <c r="K21" t="str">
-        <v>Already tested</v>
+        <v>Could create test with custom menu array missing an item</v>
       </c>
       <c r="L21" t="str">
-        <v>code analysis</v>
+        <v>Manual</v>
       </c>
       <c r="M21" t="str">
-        <v>DeepSeek</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>FH-TC-021</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Missing Scenario</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Contract</v>
-      </c>
-      <c r="D22" t="str">
-        <v>OpenAPI spec does not include POST /order response for 402</v>
-      </c>
-      <c r="E22" t="str">
-        <v>API documentation incomplete</v>
-      </c>
-      <c r="F22" t="str">
-        <v>Contract</v>
-      </c>
-      <c r="G22" t="str">
-        <v>openapi.json contains 402 response for /order with error schema</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Verify openapi.json content</v>
-      </c>
-      <c r="I22" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="J22" t="str">
-        <v>openapi.ts not shown in context; need to check if 402 defined</v>
-      </c>
-      <c r="K22" t="str">
-        <v>Coverage expansion: verify OpenAPI spec completeness</v>
-      </c>
-      <c r="L22" t="str">
-        <v>requirements</v>
-      </c>
-      <c r="M22" t="str">
-        <v>DeepSeek</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>FH-TC-022</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Missing Scenario</v>
-      </c>
-      <c r="C23" t="str">
-        <v>API</v>
-      </c>
-      <c r="D23" t="str">
-        <v>POST /order with missing paymentToken field</v>
-      </c>
-      <c r="E23" t="str">
-        <v>Zod validation should catch missing field</v>
-      </c>
-      <c r="F23" t="str">
-        <v>Integration</v>
-      </c>
-      <c r="G23" t="str">
-        <v>400 error with details about missing paymentToken</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Payload with all fields except paymentToken</v>
-      </c>
-      <c r="I23" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="J23" t="str">
-        <v>orderSchema likely requires paymentToken (not shown but inferred)</v>
-      </c>
-      <c r="K23" t="str">
-        <v>Not tested; basic validation test</v>
-      </c>
-      <c r="L23" t="str">
-        <v>knowledge base</v>
-      </c>
-      <c r="M23" t="str">
-        <v>DeepSeek</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>FH-TC-023</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Coverage Expansion</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Observability</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Observability refresh command generates correct dashboard Excel</v>
-      </c>
-      <c r="E24" t="str">
-        <v>QA observability pipeline broken</v>
-      </c>
-      <c r="F24" t="str">
-        <v>Unit</v>
-      </c>
-      <c r="G24" t="str">
-        <v>qa-artifacts/FoodHub-Observability-Dashboard.xlsx is created and contains expected sheets</v>
-      </c>
-      <c r="H24" t="str">
-        <v>Run observability:refresh command</v>
-      </c>
-      <c r="I24" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="J24" t="str">
-        <v>README describes observability:refresh</v>
-      </c>
-      <c r="K24" t="str">
-        <v>Not automated in CI; could be added as integration test</v>
-      </c>
-      <c r="L24" t="str">
-        <v>requirements</v>
-      </c>
-      <c r="M24" t="str">
-        <v>DeepSeek</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>FH-TC-024</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Edge Case</v>
-      </c>
-      <c r="C25" t="str">
-        <v>UI</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Gateway page returns with 'cancelled' status</v>
-      </c>
-      <c r="E25" t="str">
-        <v>User might lose order data</v>
-      </c>
-      <c r="F25" t="str">
-        <v>E2E</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Error message 'Payment cancelled' and cart remains intact</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Simulate gateway cancellation by adding cancel parameter? Not implemented in app. Need to test via query params: gatewayStatus=cancelled</v>
-      </c>
-      <c r="I25" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="J25" t="str">
-        <v>completeReturnedPayment only handles 'paid' status; other statuses show error message</v>
-      </c>
-      <c r="K25" t="str">
-        <v>Edge case in payment return flow</v>
-      </c>
-      <c r="L25" t="str">
-        <v>code analysis</v>
-      </c>
-      <c r="M25" t="str">
-        <v>DeepSeek</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>FH-TC-025</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Coverage Expansion</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Load</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Load test snippet: health check endpoint under peak load</v>
-      </c>
-      <c r="E26" t="str">
-        <v>Health endpoint may degrade under heavy concurrent requests</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Load</v>
-      </c>
-      <c r="G26" t="str">
-        <v>p95 latency &lt; 200ms for /health requests</v>
-      </c>
-      <c r="H26" t="str">
-        <v>k6 script targeting /health only with 100 concurrent VUs</v>
-      </c>
-      <c r="I26" t="str">
-        <v>To Do</v>
-      </c>
-      <c r="J26" t="str">
-        <v>Current load test includes health, menu, order; but not isolated</v>
-      </c>
-      <c r="K26" t="str">
-        <v>Coverage expansion: isolate health check load test</v>
-      </c>
-      <c r="L26" t="str">
-        <v>knowledge base</v>
-      </c>
-      <c r="M26" t="str">
-        <v>DeepSeek</v>
+        <v>N/A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1814,525 +1513,525 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>TDS-001</v>
       </c>
       <c r="B2" t="str">
-        <v>EDGE-001</v>
+        <v>SC-EDGE-001</v>
       </c>
       <c r="C2" t="str">
         <v>Edge Case</v>
       </c>
       <c r="D2" t="str">
-        <v>JSON Payload</v>
+        <v>PaymentToken</v>
       </c>
       <c r="E2" t="str">
-        <v>createZeroQuantityOrder</v>
+        <v>createMalformedPaymentToken</v>
       </c>
       <c r="F2" t="str">
-        <v>{ "paymentToken": "gateway_paid_test", "items": [{ "menuItemId": "burger-classic", "quantity": 0 }] }</v>
+        <v>gateway_paid_card:approved-card</v>
       </c>
       <c r="G2" t="str">
-        <v>Verify that quantity of zero is rejected with 400 error</v>
+        <v>Test that a payment token missing the paymentId after the colon is rejected</v>
       </c>
       <c r="H2" t="str">
-        <v>Integration</v>
+        <v>Integration test - POST /order</v>
       </c>
       <c r="I2" t="str">
         <v>Suggested</v>
       </c>
       <c r="J2" t="str">
-        <v>AI-generated</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K2" t="str">
         <v>DeepSeek</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>TDS-002</v>
       </c>
       <c r="B3" t="str">
-        <v>EDGE-002</v>
+        <v>SC-EDGE-002</v>
       </c>
       <c r="C3" t="str">
         <v>Edge Case</v>
       </c>
       <c r="D3" t="str">
-        <v>JSON Payload</v>
+        <v>PaymentToken</v>
       </c>
       <c r="E3" t="str">
-        <v>createNegativeQuantityOrder</v>
+        <v>createTokenWithSpecialChars</v>
       </c>
       <c r="F3" t="str">
-        <v>{ "paymentToken": "gateway_paid_test", "items": [{ "menuItemId": "burger-classic", "quantity": -1 }] }</v>
+        <v>gateway_paid_card:approved%2Dcard:pay_abc!@#$</v>
       </c>
       <c r="G3" t="str">
-        <v>Verify that negative quantity is rejected with 400 error</v>
+        <v>Ensure the gateway decodes and handles special characters in cardId and paymentId</v>
       </c>
       <c r="H3" t="str">
-        <v>Integration</v>
+        <v>Integration test - POST /order</v>
       </c>
       <c r="I3" t="str">
         <v>Suggested</v>
       </c>
       <c r="J3" t="str">
-        <v>AI-generated</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K3" t="str">
         <v>DeepSeek</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>TDS-003</v>
       </c>
       <c r="B4" t="str">
-        <v>EDGE-003</v>
+        <v>SC-EDGE-003</v>
       </c>
       <c r="C4" t="str">
         <v>Edge Case</v>
       </c>
       <c r="D4" t="str">
-        <v>Token</v>
+        <v>OrderRequest</v>
       </c>
       <c r="E4" t="str">
-        <v>createNullPaymentTokenOrder</v>
+        <v>createOrderWithMaxItems</v>
       </c>
       <c r="F4" t="str">
-        <v>{ "paymentToken": null, "items": [...] }</v>
+        <v>{"items": [{"menuItemId": "burger-classic", "quantity": 20}, {"menuItemId": "wrap-veggie", "quantity": 20}, ...]}</v>
       </c>
       <c r="G4" t="str">
-        <v>Verify that null payment token is rejected by Zod validation</v>
+        <v>Test the API with a large number of different items (near payload size limits)</v>
       </c>
       <c r="H4" t="str">
-        <v>Integration</v>
+        <v>Integration or load test</v>
       </c>
       <c r="I4" t="str">
         <v>Suggested</v>
       </c>
       <c r="J4" t="str">
-        <v>AI-generated</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K4" t="str">
         <v>DeepSeek</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>TDS-004</v>
       </c>
       <c r="B5" t="str">
-        <v>EDGE-004</v>
+        <v>SC-MISS-001</v>
       </c>
       <c r="C5" t="str">
-        <v>Edge Case</v>
+        <v>Missing Scenario</v>
       </c>
       <c r="D5" t="str">
-        <v>String</v>
+        <v>OrderRequest</v>
       </c>
       <c r="E5" t="str">
-        <v>createLongCustomerNameOrder</v>
+        <v>createOrderWithoutPaymentToken</v>
       </c>
       <c r="F5" t="str">
-        <v>{"customerName": "A very long name that exceeds 100 characters..."}</v>
+        <v>{"items": [{"menuItemId": "burger-classic", "quantity": 1}], "cardId": "approved-card", "customerName": "Test"}</v>
       </c>
       <c r="G5" t="str">
-        <v>Verify that customer names longer than 256 characters are handled gracefully</v>
+        <v>Test that the API rejects orders missing the required paymentToken field</v>
       </c>
       <c r="H5" t="str">
-        <v>Integration</v>
+        <v>Integration test - POST /order</v>
       </c>
       <c r="I5" t="str">
         <v>Suggested</v>
       </c>
       <c r="J5" t="str">
-        <v>AI-generated</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K5" t="str">
         <v>DeepSeek</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>TDS-005</v>
       </c>
       <c r="B6" t="str">
-        <v>EDGE-005</v>
+        <v>SC-MISS-002</v>
       </c>
       <c r="C6" t="str">
-        <v>Edge Case</v>
+        <v>Missing Scenario</v>
       </c>
       <c r="D6" t="str">
-        <v>JSON Payload</v>
+        <v>OrderRequest</v>
       </c>
       <c r="E6" t="str">
-        <v>createBoundaryQuantityOrder</v>
+        <v>createOrderWithEmptyCustomerName</v>
       </c>
       <c r="F6" t="str">
-        <v>{ "items": [{"menuItemId": "burger-classic", "quantity": 20}] }</v>
+        <v>{"items": [{"menuItemId": "burger-classic", "quantity": 1}], "paymentToken": "...", "cardId": "approved-card", "customerName": ""}</v>
       </c>
       <c r="G6" t="str">
-        <v>Verify that maximum quantity (20) is accepted and correctly priced</v>
+        <v>Test validation of an empty customerName field</v>
       </c>
       <c r="H6" t="str">
-        <v>Integration</v>
+        <v>Integration test - POST /order</v>
       </c>
       <c r="I6" t="str">
-        <v>Implemented</v>
+        <v>Suggested</v>
       </c>
       <c r="J6" t="str">
-        <v>Manual</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K6" t="str">
-        <v>None</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>TDS-006</v>
       </c>
       <c r="B7" t="str">
-        <v>MISS-001</v>
+        <v>SC-MISS-003</v>
       </c>
       <c r="C7" t="str">
         <v>Missing Scenario</v>
       </c>
       <c r="D7" t="str">
-        <v>Token</v>
+        <v>OrderRequest</v>
       </c>
       <c r="E7" t="str">
-        <v>createTokFailPaymentOrder</v>
+        <v>createOrderWithMixedItems</v>
       </c>
       <c r="F7" t="str">
-        <v>{ "paymentToken": "tok_fail", "items": [...] }</v>
+        <v>{"items": [{"menuItemId": "burger-classic", "quantity": 1}, {"menuItemId": "invalid-item", "quantity": 2}]}</v>
       </c>
       <c r="G7" t="str">
-        <v>Cover the undocumented token 'tok_fail' that triggers payment failure</v>
+        <v>Test that the API rejects the entire order when at least one item is invalid, without a partial order</v>
       </c>
       <c r="H7" t="str">
-        <v>Integration</v>
+        <v>Integration test - POST /order</v>
       </c>
       <c r="I7" t="str">
         <v>Suggested</v>
       </c>
       <c r="J7" t="str">
-        <v>AI-generated</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K7" t="str">
         <v>DeepSeek</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>TDS-007</v>
       </c>
       <c r="B8" t="str">
-        <v>MISS-002</v>
+        <v>SC-MISS-004</v>
       </c>
       <c r="C8" t="str">
         <v>Missing Scenario</v>
       </c>
       <c r="D8" t="str">
-        <v>Token</v>
+        <v>OrderRequest</v>
       </c>
       <c r="E8" t="str">
-        <v>createTokSuccessPaymentOrder</v>
+        <v>createOrderWithDuplicateLines</v>
       </c>
       <c r="F8" t="str">
-        <v>{ "paymentToken": "tok_success", "items": [...] }</v>
+        <v>{"items": [{"menuItemId": "burger-classic", "quantity": 1}, {"menuItemId": "burger-classic", "quantity": 1}]}</v>
       </c>
       <c r="G8" t="str">
-        <v>Cover the undocumented token 'tok_success' that triggers successful payment</v>
+        <v>Test that the API accepts duplicate lines (two entries for the same item) and calculates total correctly</v>
       </c>
       <c r="H8" t="str">
-        <v>Integration</v>
+        <v>Integration test - POST /order</v>
       </c>
       <c r="I8" t="str">
-        <v>Suggested</v>
+        <v>Implemented</v>
       </c>
       <c r="J8" t="str">
-        <v>AI-generated</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K8" t="str">
         <v>DeepSeek</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>TDS-008</v>
       </c>
       <c r="B9" t="str">
-        <v>MISS-003</v>
+        <v>SC-MISS-005</v>
       </c>
       <c r="C9" t="str">
         <v>Missing Scenario</v>
       </c>
       <c r="D9" t="str">
-        <v>JSON Payload</v>
+        <v>OrderRequest</v>
       </c>
       <c r="E9" t="str">
-        <v>createEmptyCustomerNameOrder</v>
+        <v>createOrderWithReplayedTokenAcrossInstances</v>
       </c>
       <c r="F9" t="str">
-        <v>{ "customerName": "", ... }</v>
+        <v>{"paymentToken": "gateway_paid_card:approved-card:pay_abc", "cardId": "approved-card", ...}</v>
       </c>
       <c r="G9" t="str">
-        <v>Verify that empty customer name is rejected (UI validates but API should too)</v>
+        <v>Test that the same token cannot be reused across different API instances (memory scoping). Currently token reuse is checked per FakePaymentGateway instance. This tests cross-instance reuse only if the gateway is shared, else it's acceptable.</v>
       </c>
       <c r="H9" t="str">
-        <v>Integration</v>
+        <v>Integration test - POST /order</v>
       </c>
       <c r="I9" t="str">
         <v>Suggested</v>
       </c>
       <c r="J9" t="str">
-        <v>AI-generated</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K9" t="str">
         <v>DeepSeek</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>TDS-009</v>
       </c>
       <c r="B10" t="str">
-        <v>MISS-004</v>
+        <v>SC-COV-001</v>
       </c>
       <c r="C10" t="str">
-        <v>Missing Scenario</v>
+        <v>Coverage Expansion</v>
       </c>
       <c r="D10" t="str">
-        <v>JSON Payload</v>
+        <v>OrderRequest</v>
       </c>
       <c r="E10" t="str">
-        <v>createDuplicateItemOrder</v>
+        <v>createOrderFromRandomItemSet</v>
       </c>
       <c r="F10" t="str">
-        <v>{ "items": [{ "menuItemId": "burger-classic", "quantity": 1 }, { "menuItemId": "burger-classic", "quantity": 1 }] }</v>
+        <v>Created with createRandomOrder(seed), produces 1-5 items with random valid menu items and random quantities (1-20)</v>
       </c>
       <c r="G10" t="str">
-        <v>Verify that duplicate menu item lines are accepted and total is sum of both lines</v>
+        <v>Expand coverage by fuzzing order combinations within valid bounds, using deterministic seeds</v>
       </c>
       <c r="H10" t="str">
-        <v>Integration</v>
+        <v>Integration test - POST /order (parameterized test)</v>
       </c>
       <c r="I10" t="str">
         <v>Implemented</v>
       </c>
       <c r="J10" t="str">
-        <v>Manual</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K10" t="str">
-        <v>None</v>
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>TDS-010</v>
       </c>
       <c r="B11" t="str">
-        <v>MISS-005</v>
+        <v>SC-COV-002</v>
       </c>
       <c r="C11" t="str">
-        <v>Missing Scenario</v>
+        <v>Coverage Expansion</v>
       </c>
       <c r="D11" t="str">
-        <v>HTTP Method</v>
+        <v>OrderRequest</v>
       </c>
       <c r="E11" t="str">
-        <v>getOrderEndpoint</v>
+        <v>createOrderWithAiSuggestionTrigger</v>
       </c>
       <c r="F11" t="str">
-        <v>HTTP GET /order</v>
+        <v>{"items": [{"menuItemId": "burger-classic", "quantity": 1}, {"menuItemId": "fries", "quantity": 1}]}</v>
       </c>
       <c r="G11" t="str">
-        <v>Verify that GET /order returns 405 Method Not Allowed or 404</v>
+        <v>Test that the AI suggestion is included in the response when certain item combinations are ordered (e.g., burger + fries)</v>
       </c>
       <c r="H11" t="str">
-        <v>Integration</v>
+        <v>Integration test - POST /order</v>
       </c>
       <c r="I11" t="str">
         <v>Suggested</v>
       </c>
       <c r="J11" t="str">
-        <v>AI-generated</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K11" t="str">
         <v>DeepSeek</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>TDS-011</v>
       </c>
       <c r="B12" t="str">
-        <v>MISS-006</v>
+        <v>SC-EDGE-004</v>
       </c>
       <c r="C12" t="str">
-        <v>Missing Scenario</v>
+        <v>Edge Case</v>
       </c>
       <c r="D12" t="str">
-        <v>JSON Payload</v>
+        <v>OrderRequest</v>
       </c>
       <c r="E12" t="str">
-        <v>createMissingMenuItemIdOrder</v>
+        <v>createOrderWithMaximumQuantityAllItems</v>
       </c>
       <c r="F12" t="str">
-        <v>{ "items": [{ "quantity": 1 }] }</v>
+        <v>{"items": [{"menuItemId": "burger-classic", "quantity": 20}, {"menuItemId": "wrap-veggie", "quantity": 20}, {"menuItemId": "cola-zero", "quantity": 20}]}</v>
       </c>
       <c r="G12" t="str">
-        <v>Verify that missing menuItemId field triggers Zod validation error</v>
+        <v>Test the API with each item at the maximum allowable quantity (20), ensuring total calculation and payment are correct</v>
       </c>
       <c r="H12" t="str">
-        <v>Integration</v>
+        <v>Integration test - POST /order</v>
       </c>
       <c r="I12" t="str">
         <v>Suggested</v>
       </c>
       <c r="J12" t="str">
-        <v>AI-generated</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K12" t="str">
         <v>DeepSeek</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>TDS-012</v>
       </c>
       <c r="B13" t="str">
-        <v>COV-001</v>
+        <v>SC-MISS-006</v>
       </c>
       <c r="C13" t="str">
-        <v>Coverage Expansion</v>
+        <v>Missing Scenario</v>
       </c>
       <c r="D13" t="str">
-        <v>Log Entry</v>
+        <v>OrderRequest</v>
       </c>
       <c r="E13" t="str">
-        <v>createRequestLogEntry</v>
+        <v>createOrderWithDeclinedCard</v>
       </c>
       <c r="F13" t="str">
-        <v>{ "method": "POST", "path": "/order", "statusCode": 201, "durationMs": 45 }</v>
+        <v>{"paymentToken": "gateway_declined_card:declined-card:pay_123", ...}</v>
       </c>
       <c r="G13" t="str">
-        <v>Test that requestLogger writes to observability log file in non-test environment</v>
+        <v>Test that the API returns a 402 error when a declined card token is used (already covered by existing builder createDeclinedPaymentOrder)</v>
       </c>
       <c r="H13" t="str">
-        <v>Unit</v>
+        <v>Integration test - POST /order</v>
       </c>
       <c r="I13" t="str">
-        <v>Suggested</v>
+        <v>Implemented</v>
       </c>
       <c r="J13" t="str">
-        <v>AI-generated</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K13" t="str">
         <v>DeepSeek</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>TDS-013</v>
       </c>
       <c r="B14" t="str">
-        <v>COV-002</v>
+        <v>SC-COV-003</v>
       </c>
       <c r="C14" t="str">
         <v>Coverage Expansion</v>
       </c>
       <c r="D14" t="str">
-        <v>OrderRequest</v>
+        <v>E2E Order Flow</v>
       </c>
       <c r="E14" t="str">
-        <v>createOrderWithAiSuggestionTrigger</v>
+        <v>createCheckoutWithMultipleItems</v>
       </c>
       <c r="F14" t="str">
-        <v>{ "items": [{ "menuItemId": "burger-classic", "quantity": 1 }] }</v>
+        <v>{"items": [{"menuItemId": "burger-classic", "quantity": 2}, {"menuItemId": "lemonade", "quantity": 1}]}</v>
       </c>
       <c r="G14" t="str">
-        <v>Verify that AI suggestion is returned for a simple single-item order</v>
+        <v>Expand E2E coverage to verify that the UI and gateway process an order with multiple line items correctly</v>
       </c>
       <c r="H14" t="str">
-        <v>Integration</v>
+        <v>E2E test - order-flow.spec.ts</v>
       </c>
       <c r="I14" t="str">
         <v>Suggested</v>
       </c>
       <c r="J14" t="str">
-        <v>AI-generated</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K14" t="str">
         <v>DeepSeek</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>TDS-014</v>
       </c>
       <c r="B15" t="str">
-        <v>COV-003</v>
+        <v>SC-EDGE-005</v>
       </c>
       <c r="C15" t="str">
-        <v>Coverage Expansion</v>
+        <v>Edge Case</v>
       </c>
       <c r="D15" t="str">
-        <v>Mock</v>
+        <v>PaymentToken</v>
       </c>
       <c r="E15" t="str">
-        <v>createOrderRepositorySpy</v>
+        <v>createTokenWithExcessiveLength</v>
       </c>
       <c r="F15" t="str">
-        <v>Mock OrderRepository.save() and assert called with receipt</v>
+        <v>gateway_paid_card:very-long-card-id-that-might-cause-issues-in-url-encoding:...</v>
       </c>
       <c r="G15" t="str">
-        <v>Cover the optional order repository saving logic with a unit test</v>
+        <v>Check that the payment token parsing does not break on extremely long cardId or paymentId values</v>
       </c>
       <c r="H15" t="str">
-        <v>Unit</v>
+        <v>Integration or unit test on FakePaymentGateway</v>
       </c>
       <c r="I15" t="str">
         <v>Suggested</v>
       </c>
       <c r="J15" t="str">
-        <v>AI-generated</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K15" t="str">
         <v>DeepSeek</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>TDS-015</v>
       </c>
       <c r="B16" t="str">
-        <v>COV-004</v>
+        <v>SC-COV-004</v>
       </c>
       <c r="C16" t="str">
         <v>Coverage Expansion</v>
       </c>
       <c r="D16" t="str">
-        <v>JSON Payload</v>
+        <v>Menu Response</v>
       </c>
       <c r="E16" t="str">
-        <v>createMultipleItemLargeOrder</v>
+        <v>N/A (menu is static)</v>
       </c>
       <c r="F16" t="str">
-        <v>{ "items": [ { "menuItemId": "burger-classic", "quantity": 20 }, { "menuItemId": "wrap-veggie", "quantity": 20 }, { "menuItemId": "lemonade", "quantity": 20 } ] }</v>
+        <v>GET /menu -&gt; items include unavailable item "salad-crunch"</v>
       </c>
       <c r="G16" t="str">
-        <v>Stress test the API with a large multi-item order at boundary quantity</v>
+        <v>Verify that the UI correctly displays and disables sold-out items (already covered in E2E but not explicitly tested for all unavailable items)</v>
       </c>
       <c r="H16" t="str">
-        <v>Integration</v>
+        <v>E2E test - order-flow.spec.ts</v>
       </c>
       <c r="I16" t="str">
         <v>Suggested</v>
       </c>
       <c r="J16" t="str">
-        <v>AI-generated</v>
+        <v>scenario-analysis</v>
       </c>
       <c r="K16" t="str">
         <v>DeepSeek</v>
